--- a/02_Codigo/04_BattBankDesign/01_codes/01_Pnom015/CAPEX_OPEX_ROI_15.xlsx
+++ b/02_Codigo/04_BattBankDesign/01_codes/01_Pnom015/CAPEX_OPEX_ROI_15.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\04_BattBankDesign\01_codes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\04_BattBankDesign\01_codes\01_Pnom015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700F1A8B-F0D9-49FF-BAA5-C4A69971324E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E270F721-9F6D-4A59-A1F3-D54E035396E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11610" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
+    <workbookView xWindow="-28920" yWindow="-11610" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs 15%" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="74">
   <si>
     <t>Lowest Cost ($/kWh)</t>
   </si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>Cost LTO</t>
+  </si>
+  <si>
+    <t>20 años</t>
+  </si>
+  <si>
+    <t>10 años</t>
+  </si>
+  <si>
+    <t>15 años</t>
   </si>
 </sst>
 </file>
@@ -1657,14 +1666,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9148CD0-5187-4E9B-AB88-218957DBEFDE}">
-  <dimension ref="B2:L13"/>
+  <dimension ref="B1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="H1" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="K1" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" s="16"/>
+      <c r="N1" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="16"/>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>44</v>
       </c>
@@ -1682,17 +1706,30 @@
         <v>48</v>
       </c>
       <c r="I2" s="8">
-        <f>SUM(C9:L9)+SUM(C13:L13)-F2</f>
-        <v>2445271.9057673095</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+        <f>SUM($C$9:$L$9)-F2</f>
+        <v>1153542.1213406175</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="8">
+        <f>SUM($C$9:$L$9)+SUM($C$13:$G$13)-F2</f>
+        <v>2478158.13439776</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="8">
+        <f>SUM($C$9:$L$9)+SUM($C$13:$L$13)-F2</f>
+        <v>3379669.5354062933</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="10">
-        <f>0.1</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E3" t="s">
         <v>69</v>
@@ -1705,11 +1742,25 @@
         <v>49</v>
       </c>
       <c r="I3" s="8">
-        <f>SUM(C9:L9)+SUM(C13:L13)-F3</f>
-        <v>2795271.9057673095</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="I3:I4" si="0">SUM($C$9:$L$9)-F3</f>
+        <v>1503542.1213406175</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="8">
+        <f t="shared" ref="L3:L4" si="1">SUM($C$9:$L$9)+SUM($C$13:$G$13)-F3</f>
+        <v>2828158.13439776</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="8">
+        <f>SUM($C$9:$L$9)+SUM($C$13:$L$13)-F3</f>
+        <v>3729669.5354062933</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>45</v>
       </c>
@@ -1728,11 +1779,25 @@
         <v>50</v>
       </c>
       <c r="I4" s="8">
-        <f>SUM(C9:L9)+SUM(C13:L13)-F4</f>
-        <v>1325271.9057673095</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>33542.121340617537</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="8">
+        <f t="shared" si="1"/>
+        <v>1358158.13439776</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="8">
+        <f>SUM($C$9:$L$9)+SUM($C$13:$L$13)-F4</f>
+        <v>2259669.5354062933</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C7" s="16" t="s">
         <v>47</v>
       </c>
@@ -1746,7 +1811,7 @@
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C8">
         <v>1</v>
       </c>
@@ -1778,49 +1843,49 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C9" s="5">
-        <f t="shared" ref="C9:L9" si="0">$C$4/((1+$C$3)^C8)</f>
-        <v>651129.09090909082</v>
+        <f t="shared" ref="C9:L9" si="2">$C$4/((1+$C$3)^C8)</f>
+        <v>663187.03703703696</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="0"/>
-        <v>591935.5371900826</v>
+        <f t="shared" si="2"/>
+        <v>614062.07133058982</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="0"/>
-        <v>538123.2156273477</v>
+        <f t="shared" si="2"/>
+        <v>568575.99197276833</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="0"/>
-        <v>489202.92329758883</v>
+        <f t="shared" si="2"/>
+        <v>526459.25182663731</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="0"/>
-        <v>444729.93027053529</v>
+        <f t="shared" si="2"/>
+        <v>487462.27020984935</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="0"/>
-        <v>404299.93660957745</v>
+        <f t="shared" si="2"/>
+        <v>451353.95389800856</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>367545.39691779763</v>
+        <f t="shared" si="2"/>
+        <v>417920.32768334128</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="0"/>
-        <v>334132.1790161797</v>
+        <f t="shared" si="2"/>
+        <v>386963.26637346414</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="0"/>
-        <v>303756.52637834515</v>
+        <f t="shared" si="2"/>
+        <v>358299.32071617048</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="0"/>
-        <v>276142.2967075865</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>331758.63029275043</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C12">
         <v>11</v>
       </c>
@@ -1852,51 +1917,54 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C13" s="5">
-        <f t="shared" ref="C13:L13" si="1">$C$4/((1+$C$3)^C12)</f>
-        <v>251038.4515523513</v>
+        <f t="shared" ref="C13:L13" si="3">$C$4/((1+$C$3)^C12)</f>
+        <v>307183.91693773185</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="1"/>
-        <v>228216.77413850121</v>
+        <f t="shared" si="3"/>
+        <v>284429.5527201221</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="1"/>
-        <v>207469.79467136471</v>
+        <f t="shared" si="3"/>
+        <v>263360.69696307601</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="1"/>
-        <v>188608.90424669517</v>
+        <f t="shared" si="3"/>
+        <v>243852.49718803327</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="1"/>
-        <v>171462.64022426834</v>
+        <f t="shared" si="3"/>
+        <v>225789.34924817894</v>
       </c>
       <c r="H13" s="5">
-        <f t="shared" si="1"/>
-        <v>155875.12747660757</v>
+        <f t="shared" si="3"/>
+        <v>209064.21226683239</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="1"/>
-        <v>141704.66134237053</v>
+        <f t="shared" si="3"/>
+        <v>193577.97432114108</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="1"/>
-        <v>128822.41940215501</v>
+        <f t="shared" si="3"/>
+        <v>179238.86511216764</v>
       </c>
       <c r="K13" s="5">
-        <f t="shared" si="1"/>
-        <v>117111.29036559543</v>
+        <f t="shared" si="3"/>
+        <v>165961.91214089596</v>
       </c>
       <c r="L13" s="5">
-        <f t="shared" si="1"/>
-        <v>106464.80942326858</v>
+        <f t="shared" si="3"/>
+        <v>153668.43716749627</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="C7:L7"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:O1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1905,13 +1973,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8641AB-FA05-4689-970F-41940E5E4D56}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B1:V19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="E1" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="16"/>
+      <c r="H1" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="K1" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="16"/>
+    </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>45</v>
@@ -1924,6 +2006,20 @@
         <v>51</v>
       </c>
       <c r="F2" s="11">
+        <f>IRR(B9:L9)</f>
+        <v>0.14583203543754997</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="11">
+        <f>IRR(B9:Q9)</f>
+        <v>0.17964512172791269</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="11">
         <f>IRR(B9:V9)</f>
         <v>0.19005510390504865</v>
       </c>
@@ -1934,6 +2030,20 @@
         <v>55</v>
       </c>
       <c r="F3" s="11">
+        <f>IRR(B14:L14)</f>
+        <v>0.17284089361257693</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="11">
+        <f>IRR(B14:Q14)</f>
+        <v>0.20338439889657356</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="11">
         <f>IRR(B14:V14)</f>
         <v>0.21226254296401237</v>
       </c>
@@ -1943,6 +2053,20 @@
         <v>56</v>
       </c>
       <c r="F4" s="11">
+        <f>IRR(B19:L19)</f>
+        <v>8.1555704598693213E-2</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="11">
+        <f>IRR(B19:Q19)</f>
+        <v>0.12413179874637659</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="11">
         <f>IRR(B19:V19)</f>
         <v>0.13895488560750513</v>
       </c>
@@ -2443,10 +2567,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="C7:L7"/>
     <mergeCell ref="C12:L12"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +2718,7 @@
         <v>-3001370.9090909092</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" ref="C9:L9" si="1">$C$4/((1+$C$3)^D8)+C9</f>
+        <f t="shared" ref="D9:L9" si="1">$C$4/((1+$C$3)^D8)+C9</f>
         <v>-2409435.3719008267</v>
       </c>
       <c r="E9" s="5">

--- a/02_Codigo/04_BattBankDesign/01_codes/01_Pnom015/CAPEX_OPEX_ROI_15.xlsx
+++ b/02_Codigo/04_BattBankDesign/01_codes/01_Pnom015/CAPEX_OPEX_ROI_15.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\04_BattBankDesign\01_codes\01_Pnom015\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell PC\Desktop\Tesis Magister\02_Codigo\04_BattBankDesign\01_codes\01_Pnom015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E270F721-9F6D-4A59-A1F3-D54E035396E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1235CD8B-0E1D-4587-AD6D-EEDAA46840DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11610" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs 15%" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="84">
   <si>
     <t>Lowest Cost ($/kWh)</t>
   </si>
@@ -136,18 +136,6 @@
     <t>Conventional Tug</t>
   </si>
   <si>
-    <t>Lowest yearly fuel consumption (L)</t>
-  </si>
-  <si>
-    <t>Highest yearly fuel consumption (L)</t>
-  </si>
-  <si>
-    <t>Average yearly fuel consumption (L)</t>
-  </si>
-  <si>
-    <t>Hybrid Tug</t>
-  </si>
-  <si>
     <t>Fuel Cost ($/L)</t>
   </si>
   <si>
@@ -172,15 +160,9 @@
     <t>OPEX Hybrid Tug</t>
   </si>
   <si>
-    <t>Yearly profit</t>
-  </si>
-  <si>
     <t>Lifespan</t>
   </si>
   <si>
-    <t>Yearly Profit ($)</t>
-  </si>
-  <si>
     <t>Discount Rate (%)</t>
   </si>
   <si>
@@ -238,15 +220,6 @@
     <t>Costo Total</t>
   </si>
   <si>
-    <t>Lowest yearly CO2 emissions generated (t)</t>
-  </si>
-  <si>
-    <t>Highest yearly CO2 emissions generated (t)</t>
-  </si>
-  <si>
-    <t>Average yearly CO2 emissions generated (t)</t>
-  </si>
-  <si>
     <t>Cost NMC</t>
   </si>
   <si>
@@ -263,15 +236,73 @@
   </si>
   <si>
     <t>15 años</t>
+  </si>
+  <si>
+    <t>Annual Profit ($)</t>
+  </si>
+  <si>
+    <t>Annual profit</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Battery Maintenance</t>
+  </si>
+  <si>
+    <t>Lowest annual fuel consumption (L)</t>
+  </si>
+  <si>
+    <t>Highest annual fuel consumption (L)</t>
+  </si>
+  <si>
+    <t>Average annual fuel consumption (L)</t>
+  </si>
+  <si>
+    <t>Lowest annual CO2 emissions generated (t)</t>
+  </si>
+  <si>
+    <t>Highest annual CO2 emissions generated (t)</t>
+  </si>
+  <si>
+    <t>Average annual CO2 emissions generated (t)</t>
+  </si>
+  <si>
+    <t>Hybrid Tug - NMC</t>
+  </si>
+  <si>
+    <t>Hybrid Tug - LFP</t>
+  </si>
+  <si>
+    <t>Hybrid Tug - LTO</t>
+  </si>
+  <si>
+    <t>Total OPEX - NMC</t>
+  </si>
+  <si>
+    <t>Total OPEX - LFP</t>
+  </si>
+  <si>
+    <t>Total OPEX - LTO</t>
+  </si>
+  <si>
+    <t>Anual Profit NMC ($)</t>
+  </si>
+  <si>
+    <t>Anual Profit LFP ($)</t>
+  </si>
+  <si>
+    <t>Anual Profit LTO ($)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0.0_ ;_ &quot;$&quot;* \-#,##0.0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;* #,##0.0_ ;_ &quot;$&quot;* \-#,##0.0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -334,30 +365,35 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -697,27 +733,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC14D7A-AB81-456B-B0DB-733EF237E819}">
-  <dimension ref="B3:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B3:H29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="16" t="s">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>7</v>
       </c>
@@ -734,7 +771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -742,21 +779,21 @@
         <v>2800</v>
       </c>
       <c r="D5">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="E5">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="F5">
         <f>(D5+E5)/2</f>
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="G5" s="4">
         <f>F5*C5</f>
-        <v>1820000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+        <v>2240000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -764,21 +801,21 @@
         <v>2800</v>
       </c>
       <c r="D6">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="E6">
         <v>600</v>
       </c>
       <c r="F6">
         <f t="shared" ref="F6:F7" si="0">(D6+E6)/2</f>
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" ref="G6:G7" si="1">F6*C6</f>
-        <v>1470000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+        <v>1260000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -786,31 +823,31 @@
         <v>2800</v>
       </c>
       <c r="D7">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E7">
         <v>1200</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="1"/>
-        <v>2940000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="16" t="s">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -830,7 +867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>4</v>
       </c>
@@ -841,28 +878,28 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="F10">
         <f>(D10+E10)/2</f>
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="G10" s="4">
         <f>B10*C10*F10</f>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B11" s="16" t="s">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -882,7 +919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -893,21 +930,21 @@
         <v>300</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="F13">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="G13">
         <f>(E13+F13)/2</f>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="H13" s="4">
         <f>C13*D13*G13</f>
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>14</v>
       </c>
@@ -921,29 +958,29 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G14">
         <f>(E14+F14)/2</f>
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="H14" s="4">
         <f>C14*D14*G14</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="16" t="s">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>10</v>
       </c>
@@ -963,7 +1000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C17">
         <v>1</v>
       </c>
@@ -985,17 +1022,17 @@
         <v>825000</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="16" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>10</v>
       </c>
@@ -1015,7 +1052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -1040,17 +1077,17 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="16" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
         <v>22</v>
       </c>
@@ -1064,7 +1101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E23" s="1">
         <v>100000</v>
       </c>
@@ -1080,17 +1117,17 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B24" s="16" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
         <v>22</v>
       </c>
@@ -1104,7 +1141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E26" s="1">
         <v>50000</v>
       </c>
@@ -1120,8 +1157,26 @@
         <v>65000</v>
       </c>
     </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B24:G24"/>
@@ -1137,97 +1192,97 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29A8CAA-C5C8-4FF3-BA68-5F71D3D769DB}">
   <dimension ref="B3:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="45.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B3" s="16" t="s">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="E3" s="16" t="s">
+      <c r="C3" s="19"/>
+      <c r="E3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="H3" s="16" t="s">
+      <c r="F3" s="19"/>
+      <c r="H3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="16"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="I3" s="19"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="5">
         <f>'Costs 15%'!G5</f>
-        <v>1820000</v>
+        <v>2240000</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="5">
         <f>'Costs 15%'!G6</f>
-        <v>1470000</v>
+        <v>1260000</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
       </c>
       <c r="I4" s="5">
         <f>'Costs 15%'!G7</f>
-        <v>2940000</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="5">
         <f>'Costs 15%'!$G$10</f>
-        <v>75000</v>
+        <v>150000</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="5">
         <f>'Costs 15%'!$G$10</f>
-        <v>75000</v>
+        <v>150000</v>
       </c>
       <c r="H5" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="5">
         <f>'Costs 15%'!$G$10</f>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="5">
         <f>'Costs 15%'!$H$13+'Costs 15%'!$H$14</f>
-        <v>390000</v>
+        <v>580000</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="5">
         <f>'Costs 15%'!$H$13+'Costs 15%'!$H$14</f>
-        <v>390000</v>
+        <v>580000</v>
       </c>
       <c r="H6" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="5">
         <f>'Costs 15%'!$H$13+'Costs 15%'!$H$14</f>
-        <v>390000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>15</v>
       </c>
@@ -1250,7 +1305,7 @@
         <v>825000</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -1273,7 +1328,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -1296,7 +1351,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>29</v>
       </c>
@@ -1319,78 +1374,101 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C11" s="8">
         <f>SUM(C4:C10)</f>
-        <v>3652500</v>
+        <v>4337500</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F11" s="8">
         <f>SUM(F4:F10)</f>
-        <v>3302500</v>
+        <v>3357500</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I11" s="8">
         <f>SUM(I4:I10)</f>
-        <v>4772500</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B12" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="5">
+        <v>4897500</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="17">
+        <f>C11*0.035</f>
+        <v>151812.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="17">
+        <f>F11*0.035</f>
+        <v>117512.50000000001</v>
+      </c>
+      <c r="H12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="17">
+        <f>I11*0.035</f>
+        <v>171412.50000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="5">
         <f>C11*C17</f>
         <v>0</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="E13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="5">
         <f>F11*C17</f>
         <v>0</v>
       </c>
-      <c r="H12" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="H13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="5">
         <f>I11*C17</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="8">
-        <f>C11-C12</f>
-        <v>3652500</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="8">
-        <f>F11-F12</f>
-        <v>3302500</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="8">
-        <f>I11-I12</f>
-        <v>4772500</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="8">
+        <f>C11+C12-C13</f>
+        <v>4489312.5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8">
+        <f>F11-F13-F12</f>
+        <v>3239987.5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="8">
+        <f>I11-I13-I12</f>
+        <v>4726087.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C17" s="10">
         <v>0</v>
@@ -1408,257 +1486,488 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAF4CD5-5B27-45B4-BE42-4FE58799A9A6}">
-  <dimension ref="B2:F19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:L19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B2" s="16" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="E2" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="16"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C2" s="19"/>
+      <c r="E2" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="H2" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="K2" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="19"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C3" s="6">
         <f>5366*365</f>
         <v>1958590</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="F3" s="6">
         <f>2406*365</f>
         <v>878190</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="6">
+        <f>2406*365</f>
+        <v>878190</v>
+      </c>
+      <c r="K3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="6">
+        <f>2406*365</f>
+        <v>878190</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C4" s="6">
         <f>6385*365</f>
         <v>2330525</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="F4" s="6">
         <f>4268*365</f>
         <v>1557820</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="6">
+        <f>4268*365</f>
+        <v>1557820</v>
+      </c>
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="6">
+        <f>4268*365</f>
+        <v>1557820</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <f>(C3+C4)/2</f>
         <v>2144557.5</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="F5">
         <f>(F3+F4)/2</f>
         <v>1218005</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5">
+        <f>(I3+I4)/2</f>
+        <v>1218005</v>
+      </c>
+      <c r="K5" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5">
+        <f>(L3+L4)/2</f>
+        <v>1218005</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <f>14.3*365</f>
         <v>5219.5</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F6">
         <f>6.4*365</f>
         <v>2336</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6">
+        <f>6.4*365</f>
+        <v>2336</v>
+      </c>
+      <c r="K6" t="s">
+        <v>72</v>
+      </c>
+      <c r="L6">
+        <f>6.4*365</f>
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <f>17*365</f>
         <v>6205</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F7">
         <f>11.4*365</f>
         <v>4161</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7">
+        <f>11.4*365</f>
+        <v>4161</v>
+      </c>
+      <c r="K7" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7">
+        <f>11.4*365</f>
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C8">
         <f>(C6+C7)/2</f>
         <v>5712.25</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F8">
         <f>(F6+F7)/2</f>
         <v>3248.5</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8">
+        <f>(I6+I7)/2</f>
+        <v>3248.5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8">
+        <f>(L6+L7)/2</f>
+        <v>3248.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C9" s="7">
         <f>0.8</f>
         <v>0.8</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F9" s="7">
         <f>0.8</f>
         <v>0.8</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="7">
+        <f>0.8</f>
+        <v>0.8</v>
+      </c>
+      <c r="K9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="7">
+        <f>0.8</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C10" s="4">
         <f>C5*C9</f>
         <v>1715646</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F10" s="4">
         <f>F5*F9</f>
         <v>974404</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="4">
+        <f>I5*I9</f>
+        <v>974404</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="4">
+        <f>L5*L9</f>
+        <v>974404</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1">
         <v>30000</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="1">
+        <v>30000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>40000</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1">
         <v>20000</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="1">
+        <v>20000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="F13" s="1">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+        <f>'Costs 15%'!G5/15</f>
+        <v>149333.33333333334</v>
+      </c>
+      <c r="H13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="1">
+        <f>'Costs 15%'!G6/15</f>
+        <v>84000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1">
         <f>50*C8*0</f>
         <v>0</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F14" s="1">
         <f>50*F8*0</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="1">
+        <f>50*I8*0</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="1">
+        <f>50*L8*0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C15" s="9">
         <f>SUM(C10:C14)</f>
         <v>1755646</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="F15" s="9">
         <f>SUM(F10:F14)</f>
-        <v>1039404</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="5">
+        <v>1173737.3333333333</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="9">
+        <f>SUM(I10:I14)</f>
+        <v>1108404</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L15" s="9">
+        <f>SUM(L10:L14)</f>
+        <v>1024404</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="5">
         <f>C15</f>
         <v>1755646</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="H17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="5">
+        <f>C15</f>
+        <v>1755646</v>
+      </c>
+      <c r="K17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="5">
+        <f>C15</f>
+        <v>1755646</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="5">
         <f>F15</f>
-        <v>1039404</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="8">
-        <f>C17-C18</f>
-        <v>716242</v>
+        <v>1173737.3333333333</v>
+      </c>
+      <c r="H18" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="5">
+        <f>I15</f>
+        <v>1108404</v>
+      </c>
+      <c r="K18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="5">
+        <f>L15</f>
+        <v>1024404</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="8">
+        <f>F17-F18</f>
+        <v>581908.66666666674</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="8">
+        <f>I17-I18</f>
+        <v>647242</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="8">
+        <f>L17-L18</f>
+        <v>731242</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1666,297 +1975,505 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9148CD0-5187-4E9B-AB88-218957DBEFDE}">
-  <dimension ref="B1:O13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:O16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="H1" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="K1" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="L1" s="16"/>
-      <c r="N1" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="O1" s="16"/>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="H1" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="19"/>
+      <c r="K1" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="19"/>
+      <c r="N1" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="19"/>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F2" s="5">
-        <f>'CAPEX 15%'!C13</f>
-        <v>3652500</v>
+        <f>'CAPEX 15%'!C14</f>
+        <v>4489312.5</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I2" s="8">
         <f>SUM($C$9:$L$9)-F2</f>
-        <v>1153542.1213406175</v>
+        <v>-584657.97991718352</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L2" s="8">
-        <f>SUM($C$9:$L$9)+SUM($C$13:$G$13)-F2</f>
-        <v>2478158.13439776</v>
+        <f>SUM($C$9:$L$9)+SUM($C$14:$G$14)-F2</f>
+        <v>491522.33065298386</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="O2" s="8">
-        <f>SUM($C$9:$L$9)+SUM($C$13:$L$13)-F2</f>
-        <v>3379669.5354062933</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+        <f>SUM($C$9:$L$9)+SUM($C$14:$L$14)-F2</f>
+        <v>1223952.5670056045</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C3" s="10">
         <v>0.08</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F3" s="5">
-        <f>'CAPEX 15%'!F13</f>
-        <v>3302500</v>
+        <f>'CAPEX 15%'!F14</f>
+        <v>3239987.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I3" s="8">
-        <f t="shared" ref="I3:I4" si="0">SUM($C$9:$L$9)-F3</f>
-        <v>1503542.1213406175</v>
+        <f>SUM($C$10:$L$10)-F3</f>
+        <v>1103059.0048136562</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L3" s="8">
-        <f t="shared" ref="L3:L4" si="1">SUM($C$9:$L$9)+SUM($C$13:$G$13)-F3</f>
-        <v>2828158.13439776</v>
+        <f>SUM($C$10:$L$10)+SUM($C$15:$G$15)-F3</f>
+        <v>2300066.6049308386</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="O3" s="8">
-        <f>SUM($C$9:$L$9)+SUM($C$13:$L$13)-F3</f>
-        <v>3729669.5354062933</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+        <f>SUM($C$10:$L$10)+SUM($C$15:$L$15)-F3</f>
+        <v>3114729.8642922901</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C4" s="5">
-        <f>'OPEX 15%'!C19</f>
-        <v>716242</v>
+        <f>'OPEX 15%'!F19</f>
+        <v>581908.66666666674</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F4" s="5">
-        <f>'CAPEX 15%'!I13</f>
-        <v>4772500</v>
+        <f>'CAPEX 15%'!I14</f>
+        <v>4726087.5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I4" s="8">
+        <f>SUM($C$11:$L$11)-F4</f>
+        <v>180605.84232473839</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="8">
+        <f>SUM($C$11:$L$11)+SUM($C$16:$G$16)-F4</f>
+        <v>1532962.8147166539</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="8">
+        <f>SUM($C$11:$L$11)+SUM($C$16:$L$16)-F4</f>
+        <v>2453354.2465180317</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="5">
+        <f>'OPEX 15%'!I19</f>
+        <v>647242</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="5">
+        <f>'OPEX 15%'!L19</f>
+        <v>731242</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>6</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7</v>
+      </c>
+      <c r="J8" s="2">
+        <v>8</v>
+      </c>
+      <c r="K8" s="2">
+        <v>9</v>
+      </c>
+      <c r="L8" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5">
+        <f>$C$4/((1+$C$3)^C8)</f>
+        <v>538804.32098765438</v>
+      </c>
+      <c r="D9" s="5">
+        <f t="shared" ref="D9:L9" si="0">$C$4/((1+$C$3)^D8)</f>
+        <v>498892.88980338367</v>
+      </c>
+      <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>33542.121340617537</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="8">
+        <v>461937.86092905892</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>427720.24160098046</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>396037.26074164856</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="0"/>
+        <v>366701.16735337826</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>339538.11791979463</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="0"/>
+        <v>314387.14622203208</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="0"/>
+        <v>291099.20946484449</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="0"/>
+        <v>269536.3050600412</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <f>$C$5/((1+$C$3)^C8)</f>
+        <v>599298.14814814809</v>
+      </c>
+      <c r="D10" s="5">
+        <f t="shared" ref="D10:L10" si="1">$C$5/((1+$C$3)^D8)</f>
+        <v>554905.69272976671</v>
+      </c>
+      <c r="E10" s="5">
         <f t="shared" si="1"/>
-        <v>1358158.13439776</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="8">
-        <f>SUM($C$9:$L$9)+SUM($C$13:$L$13)-F4</f>
-        <v>2259669.5354062933</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C7" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
+        <v>513801.56734237663</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="1"/>
+        <v>475742.19198368199</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="1"/>
+        <v>440502.02961452038</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="1"/>
+        <v>407872.24964307435</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="1"/>
+        <v>377659.49041025405</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="1"/>
+        <v>349684.7133428278</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="1"/>
+        <v>323782.14198409981</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="1"/>
+        <v>299798.27961490722</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5">
+        <f>$C$6/((1+$C$3)^C8)</f>
+        <v>677075.92592592584</v>
+      </c>
+      <c r="D11" s="5">
+        <f t="shared" ref="D11:L11" si="2">$C$6/((1+$C$3)^D8)</f>
+        <v>626922.15363511653</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="2"/>
+        <v>580483.47558807081</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="2"/>
+        <v>537484.69961858413</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="2"/>
+        <v>497671.01816535561</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="2"/>
+        <v>460806.49830125517</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="2"/>
+        <v>426672.68361227325</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="2"/>
+        <v>395067.29964099376</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="2"/>
+        <v>365803.05522314232</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="2"/>
+        <v>338706.53261402069</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="2">
+        <v>11</v>
+      </c>
+      <c r="D13" s="2">
+        <v>12</v>
+      </c>
+      <c r="E13" s="2">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2">
+        <v>14</v>
+      </c>
+      <c r="G13" s="2">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2">
+        <v>16</v>
+      </c>
+      <c r="I13" s="2">
+        <v>17</v>
+      </c>
+      <c r="J13" s="2">
+        <v>18</v>
+      </c>
+      <c r="K13" s="2">
+        <v>19</v>
+      </c>
+      <c r="L13" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F8">
+      <c r="C14" s="5">
+        <f t="shared" ref="C14:L14" si="3">$C$4/((1+$C$3)^C13)</f>
+        <v>249570.65283337148</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" si="3"/>
+        <v>231083.93780867729</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="3"/>
+        <v>213966.6090821086</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="3"/>
+        <v>198117.230631582</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="3"/>
+        <v>183441.88021442777</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="3"/>
+        <v>169853.59279113682</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="3"/>
+        <v>157271.84517697853</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="3"/>
+        <v>145622.07886757271</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="3"/>
+        <v>134835.25821071546</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="3"/>
+        <v>124847.46130621801</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G8">
+      <c r="C15" s="5">
+        <f>$C$5/((1+$C$3)^C13)</f>
+        <v>277590.99964343262</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" ref="D15:K15" si="4">$C$5/((1+$C$3)^D13)</f>
+        <v>257028.70337354869</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="4"/>
+        <v>237989.54016069323</v>
+      </c>
+      <c r="F15" s="5">
+        <f t="shared" si="4"/>
+        <v>220360.68533397515</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" si="4"/>
+        <v>204037.67160553255</v>
+      </c>
+      <c r="H15" s="5">
+        <f t="shared" si="4"/>
+        <v>188923.77000512273</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="4"/>
+        <v>174929.41667140994</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="4"/>
+        <v>161971.68210315733</v>
+      </c>
+      <c r="K15" s="5">
+        <f t="shared" si="4"/>
+        <v>149973.77972514566</v>
+      </c>
+      <c r="L15" s="5">
+        <f>$C$5/((1+$C$3)^L13)</f>
+        <v>138864.61085661637</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <v>9</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C9" s="5">
-        <f t="shared" ref="C9:L9" si="2">$C$4/((1+$C$3)^C8)</f>
-        <v>663187.03703703696</v>
-      </c>
-      <c r="D9" s="5">
-        <f t="shared" si="2"/>
-        <v>614062.07133058982</v>
-      </c>
-      <c r="E9" s="5">
-        <f t="shared" si="2"/>
-        <v>568575.99197276833</v>
-      </c>
-      <c r="F9" s="5">
-        <f t="shared" si="2"/>
-        <v>526459.25182663731</v>
-      </c>
-      <c r="G9" s="5">
-        <f t="shared" si="2"/>
-        <v>487462.27020984935</v>
-      </c>
-      <c r="H9" s="5">
-        <f t="shared" si="2"/>
-        <v>451353.95389800856</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="2"/>
-        <v>417920.32768334128</v>
-      </c>
-      <c r="J9" s="5">
-        <f t="shared" si="2"/>
-        <v>386963.26637346414</v>
-      </c>
-      <c r="K9" s="5">
-        <f t="shared" si="2"/>
-        <v>358299.32071617048</v>
-      </c>
-      <c r="L9" s="5">
-        <f t="shared" si="2"/>
-        <v>331758.63029275043</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C12">
-        <v>11</v>
-      </c>
-      <c r="D12">
-        <v>12</v>
-      </c>
-      <c r="E12">
-        <v>13</v>
-      </c>
-      <c r="F12">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>15</v>
-      </c>
-      <c r="H12">
-        <v>16</v>
-      </c>
-      <c r="I12">
-        <v>17</v>
-      </c>
-      <c r="J12">
-        <v>18</v>
-      </c>
-      <c r="K12">
-        <v>19</v>
-      </c>
-      <c r="L12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C13" s="5">
-        <f t="shared" ref="C13:L13" si="3">$C$4/((1+$C$3)^C12)</f>
-        <v>307183.91693773185</v>
-      </c>
-      <c r="D13" s="5">
-        <f t="shared" si="3"/>
-        <v>284429.5527201221</v>
-      </c>
-      <c r="E13" s="5">
-        <f t="shared" si="3"/>
-        <v>263360.69696307601</v>
-      </c>
-      <c r="F13" s="5">
-        <f t="shared" si="3"/>
-        <v>243852.49718803327</v>
-      </c>
-      <c r="G13" s="5">
-        <f t="shared" si="3"/>
-        <v>225789.34924817894</v>
-      </c>
-      <c r="H13" s="5">
-        <f t="shared" si="3"/>
-        <v>209064.21226683239</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="3"/>
-        <v>193577.97432114108</v>
-      </c>
-      <c r="J13" s="5">
-        <f t="shared" si="3"/>
-        <v>179238.86511216764</v>
-      </c>
-      <c r="K13" s="5">
-        <f t="shared" si="3"/>
-        <v>165961.91214089596</v>
-      </c>
-      <c r="L13" s="5">
-        <f t="shared" si="3"/>
-        <v>153668.43716749627</v>
+      <c r="C16" s="5">
+        <f>$C$6/((1+$C$3)^C13)</f>
+        <v>313617.15982779692</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" ref="D16:L16" si="5">$C$6/((1+$C$3)^D13)</f>
+        <v>290386.25909981196</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="5"/>
+        <v>268876.16583315923</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="5"/>
+        <v>248959.4128084807</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="5"/>
+        <v>230517.97482266731</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="5"/>
+        <v>213442.56928024752</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="5"/>
+        <v>197632.00859282177</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="5"/>
+        <v>182992.60054890902</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" si="5"/>
+        <v>169437.59310084168</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="5"/>
+        <v>156886.6602785571</v>
       </c>
     </row>
   </sheetData>
@@ -1974,118 +2491,131 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8641AB-FA05-4689-970F-41940E5E4D56}">
   <dimension ref="B1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="E1" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="16"/>
-      <c r="H1" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="K1" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="E1" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="H1" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="19"/>
+      <c r="K1" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="19"/>
+    </row>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="5">
+        <f>'OPEX 15%'!F19</f>
+        <v>581908.66666666674</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="5">
-        <f>'OPEX 15%'!C19</f>
-        <v>716242</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="F2" s="11">
         <f>IRR(B9:L9)</f>
-        <v>0.14583203543754997</v>
+        <v>5.0184901172991569E-2</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I2" s="11">
         <f>IRR(B9:Q9)</f>
-        <v>0.17964512172791269</v>
+        <v>9.7523777393211608E-2</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L2" s="11">
         <f>IRR(B9:V9)</f>
-        <v>0.19005510390504865</v>
-      </c>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="C3" s="10"/>
+        <v>0.11489895393710015</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="5">
+        <f>'OPEX 15%'!I19</f>
+        <v>647242</v>
+      </c>
       <c r="E3" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F3" s="11">
         <f>IRR(B14:L14)</f>
-        <v>0.17284089361257693</v>
+        <v>0.15067747468153381</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I3" s="11">
         <f>IRR(B14:Q14)</f>
-        <v>0.20338439889657356</v>
+        <v>0.18388590121311066</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L3" s="11">
         <f>IRR(B14:V14)</f>
-        <v>0.21226254296401237</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.35">
+        <v>0.19400733788652991</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="5">
+        <f>'OPEX 15%'!L19</f>
+        <v>731242</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F4" s="11">
         <f>IRR(B19:L19)</f>
-        <v>8.1555704598693213E-2</v>
+        <v>8.8400235944630756E-2</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I4" s="11">
         <f>IRR(B19:Q19)</f>
-        <v>0.12413179874637659</v>
+        <v>0.12997850894452401</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="L4" s="11">
         <f>IRR(B19:V19)</f>
-        <v>0.13895488560750513</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="C7" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
+        <v>0.14427937056240059</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C7" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>0</v>
       </c>
@@ -2150,107 +2680,107 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
-        <f>-'CAPEX 15%'!C13</f>
-        <v>-3652500</v>
+        <f>-'CAPEX 15%'!C14</f>
+        <v>-4489312.5</v>
       </c>
       <c r="C9" s="5">
         <f t="shared" ref="C9:V9" si="0">$C$2</f>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="M9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
+        <v>581908.66666666674</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>716242</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="C12" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
+        <v>581908.66666666674</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C12" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>0</v>
       </c>
@@ -2315,107 +2845,107 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
-        <f>-'CAPEX 15%'!F13</f>
-        <v>-3302500</v>
+        <f>-'CAPEX 15%'!F14</f>
+        <v>-3239987.5</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" ref="C14:V14" si="1">$C$2</f>
-        <v>716242</v>
+        <f>$C$3</f>
+        <v>647242</v>
       </c>
       <c r="D14" s="5">
-        <f t="shared" si="1"/>
-        <v>716242</v>
+        <f t="shared" ref="D14:V14" si="1">$C$3</f>
+        <v>647242</v>
       </c>
       <c r="E14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="M14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="P14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="S14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="T14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
+        <v>647242</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="1"/>
-        <v>716242</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="C17" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.35">
+        <v>647242</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C17" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>0</v>
       </c>
@@ -2480,90 +3010,90 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
-        <f>-'CAPEX 15%'!I13</f>
-        <v>-4772500</v>
+        <f>-'CAPEX 15%'!I14</f>
+        <v>-4726087.5</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:V19" si="2">$C$2</f>
-        <v>716242</v>
+        <f>$C$4</f>
+        <v>731242</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="2"/>
-        <v>716242</v>
+        <f t="shared" ref="D19:V19" si="2">$C$4</f>
+        <v>731242</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="F19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="H19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="J19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="M19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="N19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="P19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="R19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="S19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="T19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="2"/>
-        <v>716242</v>
+        <v>731242</v>
       </c>
     </row>
   </sheetData>
@@ -2581,99 +3111,130 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8AEBD9-4AB4-44E4-A602-35786004721C}">
-  <dimension ref="B2:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:Y32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.1796875" customWidth="1"/>
-    <col min="12" max="12" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F2" s="5">
-        <f>'CAPEX 15%'!C13</f>
-        <v>3652500</v>
+        <f>'CAPEX 15%'!C14</f>
+        <v>4489312.5</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I2" s="12">
         <f>F2/$C$4</f>
-        <v>5.0995333979297497</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+        <v>7.7148060463096719</v>
+      </c>
+    </row>
+    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C3" s="10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F3" s="5">
-        <f>'CAPEX 15%'!F13</f>
-        <v>3302500</v>
+        <f>'CAPEX 15%'!F14</f>
+        <v>3239987.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I3" s="12">
-        <f t="shared" ref="I3:I4" si="0">F3/$C$4</f>
-        <v>4.6108717444662561</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+        <f>F3/$C$5</f>
+        <v>5.0058363023413186</v>
+      </c>
+    </row>
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C4" s="5">
-        <f>'OPEX 15%'!C19</f>
-        <v>716242</v>
+        <f>'OPEX 15%'!F19</f>
+        <v>581908.66666666674</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F4" s="5">
-        <f>'CAPEX 15%'!I13</f>
-        <v>4772500</v>
+        <f>'CAPEX 15%'!I14</f>
+        <v>4726087.5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>6.6632506890129317</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C7" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+        <f>F4/$C$6</f>
+        <v>6.4630963484044957</v>
+      </c>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="5">
+        <f>'OPEX 15%'!I19</f>
+        <v>647242</v>
+      </c>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="5">
+        <f>'OPEX 15%'!L19</f>
+        <v>731242</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C7" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="P7" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>0</v>
       </c>
@@ -2707,54 +3268,125 @@
       <c r="L8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>3</v>
+      </c>
+      <c r="S8">
+        <v>4</v>
+      </c>
+      <c r="T8">
+        <v>5</v>
+      </c>
+      <c r="U8" s="14">
+        <v>6</v>
+      </c>
+      <c r="V8">
+        <v>7</v>
+      </c>
+      <c r="W8">
+        <v>8</v>
+      </c>
+      <c r="X8">
+        <v>9</v>
+      </c>
+      <c r="Y8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <f>-F2</f>
-        <v>-3652500</v>
+        <v>-4489312.5</v>
       </c>
       <c r="C9" s="5">
-        <f>$C$4/((1+$C$3)^C8)+B9</f>
-        <v>-3001370.9090909092</v>
+        <f>$C$4*C8-$F$2</f>
+        <v>-3907403.833333333</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" ref="D9:L9" si="1">$C$4/((1+$C$3)^D8)+C9</f>
-        <v>-2409435.3719008267</v>
+        <f t="shared" ref="D9:L9" si="0">$C$4*D8-$F$2</f>
+        <v>-3325495.1666666665</v>
       </c>
       <c r="E9" s="5">
+        <f>$C$4*E8-$F$2</f>
+        <v>-2743586.5</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>-2161677.833333333</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>-1579769.166666666</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="0"/>
+        <v>-997860.49999999953</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>-415951.83333333302</v>
+      </c>
+      <c r="J9" s="13">
+        <f t="shared" si="0"/>
+        <v>165956.83333333395</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="0"/>
+        <v>747865.50000000093</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="0"/>
+        <v>1329774.1666666679</v>
+      </c>
+      <c r="O9" s="5"/>
+      <c r="P9" s="10">
+        <f>(C9/$F$2)</f>
+        <v>-0.87037911335718621</v>
+      </c>
+      <c r="Q9" s="10">
+        <f>(D9/$F$2)</f>
+        <v>-0.74075822671437253</v>
+      </c>
+      <c r="R9" s="10">
+        <f t="shared" ref="R9:Y9" si="1">(E9/$F$2)</f>
+        <v>-0.61113734007155884</v>
+      </c>
+      <c r="S9" s="10">
         <f t="shared" si="1"/>
-        <v>-1871312.1562734791</v>
-      </c>
-      <c r="F9" s="5">
+        <v>-0.48151645342874505</v>
+      </c>
+      <c r="T9" s="10">
         <f t="shared" si="1"/>
-        <v>-1382109.2329758904</v>
-      </c>
-      <c r="G9" s="5">
+        <v>-0.35189556678593126</v>
+      </c>
+      <c r="U9" s="16">
         <f t="shared" si="1"/>
-        <v>-937379.3027053551</v>
-      </c>
-      <c r="H9" s="5">
+        <v>-0.22227468014311758</v>
+      </c>
+      <c r="V9" s="10">
         <f t="shared" si="1"/>
-        <v>-533079.3660957776</v>
-      </c>
-      <c r="I9" s="5">
+        <v>-9.2653793500303894E-2</v>
+      </c>
+      <c r="W9" s="10">
+        <f>(J9/$F$2)</f>
+        <v>3.6967093142509892E-2</v>
+      </c>
+      <c r="X9" s="10">
         <f t="shared" si="1"/>
-        <v>-165533.96917797998</v>
-      </c>
-      <c r="J9" s="13">
+        <v>0.16658797978532369</v>
+      </c>
+      <c r="Y9" s="10">
         <f t="shared" si="1"/>
-        <v>168598.20983819972</v>
-      </c>
-      <c r="K9" s="5">
-        <f t="shared" si="1"/>
-        <v>472354.73621654487</v>
-      </c>
-      <c r="L9" s="5">
-        <f t="shared" si="1"/>
-        <v>748497.03292413137</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+        <v>0.29620886642813749</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>11</v>
       </c>
@@ -2785,64 +3417,146 @@
       <c r="L12">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="P12">
+        <v>11</v>
+      </c>
+      <c r="Q12">
+        <v>12</v>
+      </c>
+      <c r="R12">
+        <v>13</v>
+      </c>
+      <c r="S12">
+        <v>14</v>
+      </c>
+      <c r="T12">
+        <v>15</v>
+      </c>
+      <c r="U12">
+        <v>16</v>
+      </c>
+      <c r="V12">
+        <v>17</v>
+      </c>
+      <c r="W12">
+        <v>18</v>
+      </c>
+      <c r="X12">
+        <v>19</v>
+      </c>
+      <c r="Y12" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C13" s="5">
-        <f>$C$4/((1+$C$3)^C12)+L9</f>
-        <v>999535.48447648273</v>
+        <f>$C$4*C12-$F$2</f>
+        <v>1911682.833333334</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" ref="D13:L13" si="2">$C$4/((1+$C$3)^D12)+C13</f>
-        <v>1227752.2586149839</v>
+        <f t="shared" ref="D13:L13" si="2">$C$4*D12-$F$2</f>
+        <v>2493591.5000000009</v>
       </c>
       <c r="E13" s="5">
         <f t="shared" si="2"/>
-        <v>1435222.0532863485</v>
+        <v>3075500.1666666679</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" si="2"/>
-        <v>1623830.9575330436</v>
+        <v>3657408.833333334</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="2"/>
-        <v>1795293.597757312</v>
+        <v>4239317.5000000019</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="2"/>
-        <v>1951168.7252339195</v>
+        <v>4821226.1666666679</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>2092873.38657629</v>
+        <v>5403134.833333334</v>
       </c>
       <c r="J13" s="5">
         <f t="shared" si="2"/>
-        <v>2221695.8059784449</v>
+        <v>5985043.5000000019</v>
       </c>
       <c r="K13" s="5">
         <f t="shared" si="2"/>
-        <v>2338807.0963440402</v>
+        <v>6566952.1666666679</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="2"/>
-        <v>2445271.905767309</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+        <v>7148860.8333333358</v>
+      </c>
+      <c r="P13" s="10">
+        <f>C13/$F$2</f>
+        <v>0.42582975307095106</v>
+      </c>
+      <c r="Q13" s="10">
+        <f t="shared" ref="Q13:Y13" si="3">D13/$F$2</f>
+        <v>0.55545063971376485</v>
+      </c>
+      <c r="R13" s="10">
+        <f t="shared" si="3"/>
+        <v>0.68507152635657864</v>
+      </c>
+      <c r="S13" s="10">
+        <f t="shared" si="3"/>
+        <v>0.81469241299939221</v>
+      </c>
+      <c r="T13" s="10">
+        <f t="shared" si="3"/>
+        <v>0.94431329964220623</v>
+      </c>
+      <c r="U13" s="10">
+        <f t="shared" si="3"/>
+        <v>1.0739341862850198</v>
+      </c>
+      <c r="V13" s="10">
+        <f t="shared" si="3"/>
+        <v>1.2035550729278335</v>
+      </c>
+      <c r="W13" s="10">
+        <f t="shared" si="3"/>
+        <v>1.3331759595706474</v>
+      </c>
+      <c r="X13" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4627968462134608</v>
+      </c>
+      <c r="Y13" s="16">
+        <f t="shared" si="3"/>
+        <v>1.592417732856275</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C16" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="P16" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>0</v>
       </c>
@@ -2861,10 +3575,10 @@
       <c r="G17">
         <v>5</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="14">
         <v>6</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17">
         <v>7</v>
       </c>
       <c r="J17">
@@ -2876,54 +3590,125 @@
       <c r="L17">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>2</v>
+      </c>
+      <c r="R17">
+        <v>3</v>
+      </c>
+      <c r="S17">
+        <v>4</v>
+      </c>
+      <c r="T17" s="14">
+        <v>5</v>
+      </c>
+      <c r="U17">
+        <v>6</v>
+      </c>
+      <c r="V17">
+        <v>7</v>
+      </c>
+      <c r="W17">
+        <v>8</v>
+      </c>
+      <c r="X17">
+        <v>9</v>
+      </c>
+      <c r="Y17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <f>-F3</f>
-        <v>-3302500</v>
+        <v>-3239987.5</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18:L18" si="3">$C$4/((1+$C$3)^C17)+B18</f>
-        <v>-2651370.9090909092</v>
+        <f t="shared" ref="C18:L18" si="4">$C$5/((1+$C$3)^C17)+B18</f>
+        <v>-2592745.5</v>
       </c>
       <c r="D18" s="5">
-        <f t="shared" si="3"/>
-        <v>-2059435.3719008267</v>
+        <f t="shared" si="4"/>
+        <v>-1945503.5</v>
       </c>
       <c r="E18" s="5">
-        <f t="shared" si="3"/>
-        <v>-1521312.1562734791</v>
+        <f t="shared" si="4"/>
+        <v>-1298261.5</v>
       </c>
       <c r="F18" s="5">
-        <f t="shared" si="3"/>
-        <v>-1032109.2329758903</v>
+        <f t="shared" si="4"/>
+        <v>-651019.5</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="3"/>
-        <v>-587379.30270535499</v>
-      </c>
-      <c r="H18" s="5">
-        <f t="shared" si="3"/>
-        <v>-183079.36609577754</v>
-      </c>
-      <c r="I18" s="13">
-        <f t="shared" si="3"/>
-        <v>184466.03082202008</v>
+        <f t="shared" si="4"/>
+        <v>-3777.5</v>
+      </c>
+      <c r="H18" s="13">
+        <f t="shared" si="4"/>
+        <v>643464.5</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="4"/>
+        <v>1290706.5</v>
       </c>
       <c r="J18" s="5">
-        <f t="shared" si="3"/>
-        <v>518598.20983819978</v>
+        <f t="shared" si="4"/>
+        <v>1937948.5</v>
       </c>
       <c r="K18" s="5">
-        <f t="shared" si="3"/>
-        <v>822354.73621654487</v>
+        <f t="shared" si="4"/>
+        <v>2585190.5</v>
       </c>
       <c r="L18" s="5">
-        <f t="shared" si="3"/>
-        <v>1098497.0329241315</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>3232432.5</v>
+      </c>
+      <c r="O18" s="5"/>
+      <c r="P18" s="10">
+        <f>C18/$F$3</f>
+        <v>-0.80023317991195952</v>
+      </c>
+      <c r="Q18" s="10">
+        <f t="shared" ref="Q18:Y18" si="5">D18/$F$3</f>
+        <v>-0.60046635982391905</v>
+      </c>
+      <c r="R18" s="10">
+        <f t="shared" si="5"/>
+        <v>-0.40069953973587863</v>
+      </c>
+      <c r="S18" s="10">
+        <f t="shared" si="5"/>
+        <v>-0.20093271964783815</v>
+      </c>
+      <c r="T18" s="16">
+        <f t="shared" si="5"/>
+        <v>-1.1658995597976843E-3</v>
+      </c>
+      <c r="U18" s="10">
+        <f t="shared" si="5"/>
+        <v>0.19860092052824277</v>
+      </c>
+      <c r="V18" s="10">
+        <f t="shared" si="5"/>
+        <v>0.39836774061628322</v>
+      </c>
+      <c r="W18" s="10">
+        <f t="shared" si="5"/>
+        <v>0.59813456070432369</v>
+      </c>
+      <c r="X18" s="10">
+        <f t="shared" si="5"/>
+        <v>0.79790138079236417</v>
+      </c>
+      <c r="Y18" s="10">
+        <f t="shared" si="5"/>
+        <v>0.99766820088040464</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C21">
         <v>11</v>
       </c>
@@ -2954,64 +3739,146 @@
       <c r="L21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="P21">
+        <v>11</v>
+      </c>
+      <c r="Q21">
+        <v>12</v>
+      </c>
+      <c r="R21">
+        <v>13</v>
+      </c>
+      <c r="S21">
+        <v>14</v>
+      </c>
+      <c r="T21">
+        <v>15</v>
+      </c>
+      <c r="U21">
+        <v>16</v>
+      </c>
+      <c r="V21">
+        <v>17</v>
+      </c>
+      <c r="W21">
+        <v>18</v>
+      </c>
+      <c r="X21">
+        <v>19</v>
+      </c>
+      <c r="Y21" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C22" s="5">
-        <f>$C$4/((1+$C$3)^C21)+L18</f>
-        <v>1349535.4844764827</v>
+        <f>$C$5/((1+$C$3)^C21)+L18</f>
+        <v>3879674.5</v>
       </c>
       <c r="D22" s="5">
-        <f t="shared" ref="D22:L22" si="4">$C$4/((1+$C$3)^D21)+C22</f>
-        <v>1577752.2586149839</v>
+        <f t="shared" ref="D22:L22" si="6">$C$5/((1+$C$3)^D21)+C22</f>
+        <v>4526916.5</v>
       </c>
       <c r="E22" s="5">
-        <f t="shared" si="4"/>
-        <v>1785222.0532863485</v>
+        <f t="shared" si="6"/>
+        <v>5174158.5</v>
       </c>
       <c r="F22" s="5">
-        <f t="shared" si="4"/>
-        <v>1973830.9575330436</v>
+        <f t="shared" si="6"/>
+        <v>5821400.5</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" si="4"/>
-        <v>2145293.597757312</v>
+        <f t="shared" si="6"/>
+        <v>6468642.5</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" si="4"/>
-        <v>2301168.7252339195</v>
+        <f t="shared" si="6"/>
+        <v>7115884.5</v>
       </c>
       <c r="I22" s="5">
-        <f t="shared" si="4"/>
-        <v>2442873.3865762898</v>
+        <f t="shared" si="6"/>
+        <v>7763126.5</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" si="4"/>
-        <v>2571695.8059784449</v>
+        <f t="shared" si="6"/>
+        <v>8410368.5</v>
       </c>
       <c r="K22" s="5">
-        <f t="shared" si="4"/>
-        <v>2688807.0963440402</v>
+        <f t="shared" si="6"/>
+        <v>9057610.5</v>
       </c>
       <c r="L22" s="5">
-        <f t="shared" si="4"/>
-        <v>2795271.905767309</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>9704852.5</v>
+      </c>
+      <c r="P22" s="10">
+        <f>C22/$F$3</f>
+        <v>1.197435020968445</v>
+      </c>
+      <c r="Q22" s="10">
+        <f t="shared" ref="Q22:Y22" si="7">D22/$F$3</f>
+        <v>1.3972018410564855</v>
+      </c>
+      <c r="R22" s="10">
+        <f t="shared" si="7"/>
+        <v>1.596968661144526</v>
+      </c>
+      <c r="S22" s="10">
+        <f t="shared" si="7"/>
+        <v>1.7967354812325664</v>
+      </c>
+      <c r="T22" s="10">
+        <f t="shared" si="7"/>
+        <v>1.9965023013206069</v>
+      </c>
+      <c r="U22" s="10">
+        <f t="shared" si="7"/>
+        <v>2.1962691214086476</v>
+      </c>
+      <c r="V22" s="10">
+        <f t="shared" si="7"/>
+        <v>2.3960359414966881</v>
+      </c>
+      <c r="W22" s="10">
+        <f t="shared" si="7"/>
+        <v>2.5958027615847286</v>
+      </c>
+      <c r="X22" s="10">
+        <f t="shared" si="7"/>
+        <v>2.7955695816727686</v>
+      </c>
+      <c r="Y22" s="16">
+        <f t="shared" si="7"/>
+        <v>2.9953364017608091</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C26" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="P26" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="19"/>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0</v>
       </c>
@@ -3033,7 +3900,7 @@
       <c r="H27">
         <v>6</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="14">
         <v>7</v>
       </c>
       <c r="J27">
@@ -3045,58 +3912,129 @@
       <c r="L27">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>2</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
+      </c>
+      <c r="S27">
+        <v>4</v>
+      </c>
+      <c r="T27">
+        <v>5</v>
+      </c>
+      <c r="U27">
+        <v>6</v>
+      </c>
+      <c r="V27" s="14">
+        <v>7</v>
+      </c>
+      <c r="W27">
+        <v>8</v>
+      </c>
+      <c r="X27">
+        <v>9</v>
+      </c>
+      <c r="Y27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <f>-F4</f>
-        <v>-4772500</v>
+        <v>-4726087.5</v>
       </c>
       <c r="C28" s="5">
-        <f t="shared" ref="C28:L28" si="5">$C$4/((1+$C$3)^C27)+B28</f>
-        <v>-4121370.9090909092</v>
+        <f t="shared" ref="C28:L28" si="8">$C$6/((1+$C$3)^C27)+B28</f>
+        <v>-3994845.5</v>
       </c>
       <c r="D28" s="5">
-        <f t="shared" si="5"/>
-        <v>-3529435.3719008267</v>
+        <f t="shared" si="8"/>
+        <v>-3263603.5</v>
       </c>
       <c r="E28" s="5">
-        <f t="shared" si="5"/>
-        <v>-2991312.1562734791</v>
+        <f t="shared" si="8"/>
+        <v>-2532361.5</v>
       </c>
       <c r="F28" s="5">
-        <f t="shared" si="5"/>
-        <v>-2502109.2329758904</v>
+        <f t="shared" si="8"/>
+        <v>-1801119.5</v>
       </c>
       <c r="G28" s="5">
-        <f t="shared" si="5"/>
-        <v>-2057379.302705355</v>
+        <f t="shared" si="8"/>
+        <v>-1069877.5</v>
       </c>
       <c r="H28" s="5">
-        <f t="shared" si="5"/>
-        <v>-1653079.3660957776</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="5"/>
-        <v>-1285533.96917798</v>
+        <f t="shared" si="8"/>
+        <v>-338635.5</v>
+      </c>
+      <c r="I28" s="13">
+        <f t="shared" si="8"/>
+        <v>392606.5</v>
       </c>
       <c r="J28" s="5">
-        <f t="shared" si="5"/>
-        <v>-951401.79016180034</v>
+        <f t="shared" si="8"/>
+        <v>1123848.5</v>
       </c>
       <c r="K28" s="5">
-        <f t="shared" si="5"/>
-        <v>-647645.26378345513</v>
+        <f t="shared" si="8"/>
+        <v>1855090.5</v>
       </c>
       <c r="L28" s="5">
-        <f t="shared" si="5"/>
-        <v>-371502.96707586863</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>2586332.5</v>
+      </c>
+      <c r="O28" s="5"/>
+      <c r="P28" s="10">
+        <f>C28/$F$4</f>
+        <v>-0.84527539957734599</v>
+      </c>
+      <c r="Q28" s="10">
+        <f t="shared" ref="Q28:Y28" si="9">D28/$F$4</f>
+        <v>-0.69055079915469186</v>
+      </c>
+      <c r="R28" s="10">
+        <f t="shared" si="9"/>
+        <v>-0.53582619873203785</v>
+      </c>
+      <c r="S28" s="10">
+        <f t="shared" si="9"/>
+        <v>-0.38110159830938384</v>
+      </c>
+      <c r="T28" s="10">
+        <f t="shared" si="9"/>
+        <v>-0.22637699788672977</v>
+      </c>
+      <c r="U28" s="10">
+        <f t="shared" si="9"/>
+        <v>-7.1652397464075729E-2</v>
+      </c>
+      <c r="V28" s="16">
+        <f t="shared" si="9"/>
+        <v>8.3072202958578312E-2</v>
+      </c>
+      <c r="W28" s="10">
+        <f t="shared" si="9"/>
+        <v>0.23779680338123235</v>
+      </c>
+      <c r="X28" s="10">
+        <f t="shared" si="9"/>
+        <v>0.39252140380388639</v>
+      </c>
+      <c r="Y28" s="10">
+        <f t="shared" si="9"/>
+        <v>0.54724600422654046</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C31">
         <v>11</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31">
         <v>12</v>
       </c>
       <c r="E31">
@@ -3123,54 +4061,127 @@
       <c r="L31">
         <v>20</v>
       </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="P31">
+        <v>11</v>
+      </c>
+      <c r="Q31">
+        <v>12</v>
+      </c>
+      <c r="R31">
+        <v>13</v>
+      </c>
+      <c r="S31">
+        <v>14</v>
+      </c>
+      <c r="T31">
+        <v>15</v>
+      </c>
+      <c r="U31">
+        <v>16</v>
+      </c>
+      <c r="V31">
+        <v>17</v>
+      </c>
+      <c r="W31">
+        <v>18</v>
+      </c>
+      <c r="X31">
+        <v>19</v>
+      </c>
+      <c r="Y31" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C32" s="5">
-        <f>$C$4/((1+$C$3)^C31)+L28</f>
-        <v>-120464.51552351733</v>
-      </c>
-      <c r="D32" s="13">
-        <f t="shared" ref="D32:L32" si="6">$C$4/((1+$C$3)^D31)+C32</f>
-        <v>107752.25861498388</v>
+        <f>$C$6/((1+$C$3)^C31)+L28</f>
+        <v>3317574.5</v>
+      </c>
+      <c r="D32" s="5">
+        <f t="shared" ref="D32:L32" si="10">$C$6/((1+$C$3)^D31)+C32</f>
+        <v>4048816.5</v>
       </c>
       <c r="E32" s="5">
-        <f t="shared" si="6"/>
-        <v>315222.05328634859</v>
+        <f t="shared" si="10"/>
+        <v>4780058.5</v>
       </c>
       <c r="F32" s="5">
-        <f t="shared" si="6"/>
-        <v>503830.95753304375</v>
+        <f t="shared" si="10"/>
+        <v>5511300.5</v>
       </c>
       <c r="G32" s="5">
-        <f t="shared" si="6"/>
-        <v>675293.59775731212</v>
+        <f t="shared" si="10"/>
+        <v>6242542.5</v>
       </c>
       <c r="H32" s="5">
-        <f t="shared" si="6"/>
-        <v>831168.72523391969</v>
+        <f t="shared" si="10"/>
+        <v>6973784.5</v>
       </c>
       <c r="I32" s="5">
-        <f t="shared" si="6"/>
-        <v>972873.38657629024</v>
+        <f t="shared" si="10"/>
+        <v>7705026.5</v>
       </c>
       <c r="J32" s="5">
-        <f t="shared" si="6"/>
-        <v>1101695.8059784453</v>
+        <f t="shared" si="10"/>
+        <v>8436268.5</v>
       </c>
       <c r="K32" s="5">
-        <f t="shared" si="6"/>
-        <v>1218807.0963440407</v>
+        <f t="shared" si="10"/>
+        <v>9167510.5</v>
       </c>
       <c r="L32" s="5">
-        <f t="shared" si="6"/>
-        <v>1325271.9057673092</v>
+        <f t="shared" si="10"/>
+        <v>9898752.5</v>
+      </c>
+      <c r="P32" s="10">
+        <f>C32/$F$4</f>
+        <v>0.70197060464919447</v>
+      </c>
+      <c r="Q32" s="10">
+        <f t="shared" ref="Q32:Y32" si="11">D32/$F$4</f>
+        <v>0.8566952050718486</v>
+      </c>
+      <c r="R32" s="10">
+        <f t="shared" si="11"/>
+        <v>1.0114198054945025</v>
+      </c>
+      <c r="S32" s="10">
+        <f t="shared" si="11"/>
+        <v>1.1661444059171566</v>
+      </c>
+      <c r="T32" s="10">
+        <f t="shared" si="11"/>
+        <v>1.3208690063398107</v>
+      </c>
+      <c r="U32" s="10">
+        <f t="shared" si="11"/>
+        <v>1.4755936067624646</v>
+      </c>
+      <c r="V32" s="10">
+        <f t="shared" si="11"/>
+        <v>1.6303182071851188</v>
+      </c>
+      <c r="W32" s="10">
+        <f t="shared" si="11"/>
+        <v>1.7850428076077729</v>
+      </c>
+      <c r="X32" s="10">
+        <f t="shared" si="11"/>
+        <v>1.9397674080304268</v>
+      </c>
+      <c r="Y32" s="16">
+        <f t="shared" si="11"/>
+        <v>2.0944920084530807</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="C7:L7"/>
     <mergeCell ref="C16:L16"/>
     <mergeCell ref="C26:L26"/>
+    <mergeCell ref="P7:Y7"/>
+    <mergeCell ref="P16:Y16"/>
+    <mergeCell ref="P26:Y26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/02_Codigo/04_BattBankDesign/01_codes/01_Pnom015/CAPEX_OPEX_ROI_15.xlsx
+++ b/02_Codigo/04_BattBankDesign/01_codes/01_Pnom015/CAPEX_OPEX_ROI_15.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell PC\Desktop\Tesis Magister\02_Codigo\04_BattBankDesign\01_codes\01_Pnom015\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\04_BattBankDesign\01_codes\01_Pnom015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1235CD8B-0E1D-4587-AD6D-EEDAA46840DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A5EA82-37FD-43AC-A0AB-2F6C7B782871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
+    <workbookView xWindow="-28920" yWindow="-11610" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs 15%" sheetId="1" r:id="rId1"/>
@@ -238,9 +238,6 @@
     <t>15 años</t>
   </si>
   <si>
-    <t>Annual Profit ($)</t>
-  </si>
-  <si>
     <t>Annual profit</t>
   </si>
   <si>
@@ -293,6 +290,9 @@
   </si>
   <si>
     <t>Anual Profit LTO ($)</t>
+  </si>
+  <si>
+    <t>Annual Profit NMC ($)</t>
   </si>
 </sst>
 </file>
@@ -300,8 +300,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_ &quot;$&quot;* #,##0.0_ ;_ &quot;$&quot;* \-#,##0.0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -365,32 +365,32 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="42" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -734,17 +734,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC14D7A-AB81-456B-B0DB-733EF237E819}">
   <dimension ref="B3:H29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3" s="19" t="s">
         <v>2</v>
       </c>
@@ -754,7 +754,7 @@
       <c r="F3" s="19"/>
       <c r="G3" s="19"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>7</v>
       </c>
@@ -771,7 +771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -793,7 +793,7 @@
         <v>2240000</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -815,7 +815,7 @@
         <v>1260000</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -837,7 +837,7 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="19" t="s">
         <v>9</v>
       </c>
@@ -847,7 +847,7 @@
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -867,7 +867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>4</v>
       </c>
@@ -889,7 +889,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B11" s="19" t="s">
         <v>12</v>
       </c>
@@ -899,7 +899,7 @@
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -919,7 +919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -944,7 +944,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>14</v>
       </c>
@@ -969,7 +969,7 @@
         <v>370000</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B15" s="19" t="s">
         <v>15</v>
       </c>
@@ -980,7 +980,7 @@
       <c r="G15" s="19"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
         <v>10</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C17">
         <v>1</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>825000</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" s="19" t="s">
         <v>16</v>
       </c>
@@ -1032,7 +1032,7 @@
       <c r="F18" s="19"/>
       <c r="G18" s="19"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
         <v>10</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B21" s="19" t="s">
         <v>20</v>
       </c>
@@ -1087,7 +1087,7 @@
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E22" t="s">
         <v>22</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E23" s="1">
         <v>100000</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24" s="19" t="s">
         <v>21</v>
       </c>
@@ -1127,7 +1127,7 @@
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E25" t="s">
         <v>22</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E26" s="1">
         <v>50000</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -1165,10 +1165,10 @@
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1192,14 +1192,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29A8CAA-C5C8-4FF3-BA68-5F71D3D769DB}">
   <dimension ref="B3:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" s="19" t="s">
         <v>3</v>
       </c>
@@ -1213,7 +1216,7 @@
       </c>
       <c r="I3" s="19"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>25</v>
       </c>
@@ -1236,7 +1239,7 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>26</v>
       </c>
@@ -1259,7 +1262,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>27</v>
       </c>
@@ -1282,7 +1285,7 @@
         <v>580000</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>15</v>
       </c>
@@ -1305,7 +1308,7 @@
         <v>825000</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -1351,7 +1354,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>29</v>
       </c>
@@ -1374,7 +1377,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>57</v>
       </c>
@@ -1397,81 +1400,81 @@
         <v>4897500</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="17">
         <f>C11*0.035</f>
         <v>151812.5</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12" s="17">
         <f>F11*0.035</f>
         <v>117512.50000000001</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" s="17">
         <f>I11*0.035</f>
         <v>171412.50000000003</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="5">
         <f>C11*C17</f>
-        <v>0</v>
+        <v>433750</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>55</v>
       </c>
       <c r="F13" s="5">
         <f>F11*C17</f>
-        <v>0</v>
+        <v>335750</v>
       </c>
       <c r="H13" s="14" t="s">
         <v>55</v>
       </c>
       <c r="I13" s="5">
         <f>I11*C17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+        <v>489750</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="8">
         <f>C11+C12-C13</f>
-        <v>4489312.5</v>
+        <v>4055562.5</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F14" s="8">
         <f>F11-F13-F12</f>
-        <v>3239987.5</v>
+        <v>2904237.5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>58</v>
       </c>
       <c r="I14" s="8">
         <f>I11-I13-I12</f>
-        <v>4726087.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+        <v>4236337.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C17" s="10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1487,215 +1490,215 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAF4CD5-5B27-45B4-BE42-4FE58799A9A6}">
   <dimension ref="B2:L19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B2" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C2" s="19"/>
       <c r="E2" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="19"/>
       <c r="H2" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I2" s="19"/>
       <c r="K2" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L2" s="19"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="6">
         <f>5366*365</f>
         <v>1958590</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3" s="6">
         <f>2406*365</f>
         <v>878190</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I3" s="6">
         <f>2406*365</f>
         <v>878190</v>
       </c>
       <c r="K3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L3" s="6">
         <f>2406*365</f>
         <v>878190</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="6">
         <f>6385*365</f>
         <v>2330525</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4" s="6">
         <f>4268*365</f>
         <v>1557820</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I4" s="6">
         <f>4268*365</f>
         <v>1557820</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L4" s="6">
         <f>4268*365</f>
         <v>1557820</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <f>(C3+C4)/2</f>
         <v>2144557.5</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <f>(F3+F4)/2</f>
         <v>1218005</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I5">
         <f>(I3+I4)/2</f>
         <v>1218005</v>
       </c>
       <c r="K5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L5">
         <f>(L3+L4)/2</f>
         <v>1218005</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <f>14.3*365</f>
         <v>5219.5</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F6">
         <f>6.4*365</f>
         <v>2336</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I6">
         <f>6.4*365</f>
         <v>2336</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L6">
         <f>6.4*365</f>
         <v>2336</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <f>17*365</f>
         <v>6205</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <f>11.4*365</f>
         <v>4161</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I7">
         <f>11.4*365</f>
         <v>4161</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L7">
         <f>11.4*365</f>
         <v>4161</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8">
         <f>(C6+C7)/2</f>
         <v>5712.25</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8">
         <f>(F6+F7)/2</f>
         <v>3248.5</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I8">
         <f>(I6+I7)/2</f>
         <v>3248.5</v>
       </c>
       <c r="K8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L8">
         <f>(L6+L7)/2</f>
         <v>3248.5</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>31</v>
       </c>
@@ -1725,7 +1728,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>32</v>
       </c>
@@ -1755,7 +1758,7 @@
         <v>974404</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>33</v>
       </c>
@@ -1781,7 +1784,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>34</v>
       </c>
@@ -1807,7 +1810,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -1815,151 +1818,151 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F13" s="1">
         <f>'Costs 15%'!G5/15</f>
         <v>149333.33333333334</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I13" s="1">
         <f>'Costs 15%'!G6/15</f>
         <v>84000</v>
       </c>
       <c r="K13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="15" t="s">
         <v>54</v>
       </c>
       <c r="C14" s="1">
-        <f>50*C8*0</f>
-        <v>0</v>
+        <f>50*C8</f>
+        <v>285612.5</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>54</v>
       </c>
       <c r="F14" s="1">
-        <f>50*F8*0</f>
-        <v>0</v>
+        <f>50*F8</f>
+        <v>162425</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>54</v>
       </c>
       <c r="I14" s="1">
-        <f>50*I8*0</f>
-        <v>0</v>
+        <f>50*I8</f>
+        <v>162425</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>54</v>
       </c>
       <c r="L14" s="1">
-        <f>50*L8*0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+        <f>50*L8</f>
+        <v>162425</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="9">
         <f>SUM(C10:C14)</f>
-        <v>1755646</v>
+        <v>2041258.5</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" s="9">
         <f>SUM(F10:F14)</f>
-        <v>1173737.3333333333</v>
+        <v>1336162.3333333333</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I15" s="9">
         <f>SUM(I10:I14)</f>
-        <v>1108404</v>
+        <v>1270829</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L15" s="9">
         <f>SUM(L10:L14)</f>
-        <v>1024404</v>
-      </c>
-    </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+        <v>1186829</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.35">
       <c r="E17" t="s">
         <v>37</v>
       </c>
       <c r="F17" s="5">
         <f>C15</f>
-        <v>1755646</v>
+        <v>2041258.5</v>
       </c>
       <c r="H17" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="5">
         <f>C15</f>
-        <v>1755646</v>
+        <v>2041258.5</v>
       </c>
       <c r="K17" t="s">
         <v>37</v>
       </c>
       <c r="L17" s="5">
         <f>C15</f>
-        <v>1755646</v>
-      </c>
-    </row>
-    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
+        <v>2041258.5</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.35">
       <c r="E18" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="5">
         <f>F15</f>
-        <v>1173737.3333333333</v>
+        <v>1336162.3333333333</v>
       </c>
       <c r="H18" t="s">
         <v>38</v>
       </c>
       <c r="I18" s="5">
         <f>I15</f>
-        <v>1108404</v>
+        <v>1270829</v>
       </c>
       <c r="K18" t="s">
         <v>38</v>
       </c>
       <c r="L18" s="5">
         <f>L15</f>
-        <v>1024404</v>
-      </c>
-    </row>
-    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
+        <v>1186829</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.35">
       <c r="E19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F19" s="8">
         <f>F17-F18</f>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" s="8">
         <f>I17-I18</f>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L19" s="8">
         <f>L17-L18</f>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
     </row>
   </sheetData>
@@ -1976,14 +1979,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9148CD0-5187-4E9B-AB88-218957DBEFDE}">
   <dimension ref="B1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
       <c r="H1" s="19" t="s">
         <v>63</v>
       </c>
@@ -1997,7 +2000,7 @@
       </c>
       <c r="O1" s="19"/>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>39</v>
       </c>
@@ -2009,31 +2012,31 @@
       </c>
       <c r="F2" s="5">
         <f>'CAPEX 15%'!C14</f>
-        <v>4489312.5</v>
+        <v>4055562.5</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="I2" s="8">
         <f>SUM($C$9:$L$9)-F2</f>
-        <v>-584657.97991718352</v>
+        <v>675690.17241491564</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L2" s="8">
         <f>SUM($C$9:$L$9)+SUM($C$14:$G$14)-F2</f>
-        <v>491522.33065298386</v>
+        <v>1979693.1115219137</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="O2" s="8">
         <f>SUM($C$9:$L$9)+SUM($C$14:$L$14)-F2</f>
-        <v>1223952.5670056045</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+        <v>2867175.6007607644</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>40</v>
       </c>
@@ -2045,86 +2048,86 @@
       </c>
       <c r="F3" s="5">
         <f>'CAPEX 15%'!F14</f>
-        <v>3239987.5</v>
+        <v>2904237.5</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="I3" s="8">
         <f>SUM($C$10:$L$10)-F3</f>
-        <v>1103059.0048136562</v>
+        <v>2265407.1571457563</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="8">
         <f>SUM($C$10:$L$10)+SUM($C$15:$G$15)-F3</f>
-        <v>2300066.6049308386</v>
+        <v>3690237.3857997693</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="O3" s="8">
         <f>SUM($C$10:$L$10)+SUM($C$15:$L$15)-F3</f>
-        <v>3114729.8642922901</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+        <v>4659952.8980474509</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="5">
         <f>'OPEX 15%'!F19</f>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="E4" t="s">
         <v>61</v>
       </c>
       <c r="F4" s="5">
         <f>'CAPEX 15%'!I14</f>
-        <v>4726087.5</v>
+        <v>4236337.5</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="I4" s="8">
         <f>SUM($C$11:$L$11)-F4</f>
-        <v>180605.84232473839</v>
+        <v>1496953.9946568366</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="L4" s="8">
         <f>SUM($C$11:$L$11)+SUM($C$16:$G$16)-F4</f>
-        <v>1532962.8147166539</v>
+        <v>3077133.5955855828</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="O4" s="8">
         <f>SUM($C$11:$L$11)+SUM($C$16:$L$16)-F4</f>
-        <v>2453354.2465180317</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+        <v>4152577.2802731898</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="5">
         <f>'OPEX 15%'!I19</f>
-        <v>647242</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+        <v>770429.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5">
         <f>'OPEX 15%'!L19</f>
-        <v>731242</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+        <v>854429.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C7" s="19" t="s">
         <v>41</v>
       </c>
@@ -2138,7 +2141,7 @@
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C8" s="2">
         <v>1</v>
       </c>
@@ -2170,145 +2173,145 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="18" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="5">
         <f>$C$4/((1+$C$3)^C8)</f>
-        <v>538804.32098765438</v>
+        <v>652866.82098765438</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" ref="D9:L9" si="0">$C$4/((1+$C$3)^D8)</f>
-        <v>498892.88980338367</v>
+        <v>604506.31572930957</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>461937.86092905892</v>
+        <v>559728.07011973101</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>427720.24160098046</v>
+        <v>518266.73159234354</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>396037.26074164856</v>
+        <v>479876.60332624399</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
-        <v>366701.16735337826</v>
+        <v>444330.18826504069</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>339538.11791979463</v>
+        <v>411416.84098614875</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="0"/>
-        <v>314387.14622203208</v>
+        <v>380941.51943161921</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>291099.20946484449</v>
+        <v>352723.62910335109</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>269536.3050600412</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+        <v>326595.95287347323</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="18" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5">
         <f>$C$5/((1+$C$3)^C8)</f>
-        <v>599298.14814814809</v>
+        <v>713360.64814814809</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" ref="D10:L10" si="1">$C$5/((1+$C$3)^D8)</f>
-        <v>554905.69272976671</v>
+        <v>660519.11865569267</v>
       </c>
       <c r="E10" s="5">
         <f t="shared" si="1"/>
-        <v>513801.56734237663</v>
+        <v>611591.77653304872</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" si="1"/>
-        <v>475742.19198368199</v>
+        <v>566288.68197504513</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="1"/>
-        <v>440502.02961452038</v>
+        <v>524341.37219911581</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
-        <v>407872.24964307435</v>
+        <v>485501.27055473678</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="1"/>
-        <v>377659.49041025405</v>
+        <v>449538.21347660816</v>
       </c>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>349684.7133428278</v>
+        <v>416239.08655241493</v>
       </c>
       <c r="K10" s="5">
         <f t="shared" si="1"/>
-        <v>323782.14198409981</v>
+        <v>385406.56162260642</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="1"/>
-        <v>299798.27961490722</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+        <v>356857.92742833926</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="18" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="5">
         <f>$C$6/((1+$C$3)^C8)</f>
-        <v>677075.92592592584</v>
+        <v>791138.42592592584</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" ref="D11:L11" si="2">$C$6/((1+$C$3)^D8)</f>
-        <v>626922.15363511653</v>
+        <v>732535.57956104248</v>
       </c>
       <c r="E11" s="5">
         <f t="shared" si="2"/>
-        <v>580483.47558807081</v>
+        <v>678273.68477874296</v>
       </c>
       <c r="F11" s="5">
         <f t="shared" si="2"/>
-        <v>537484.69961858413</v>
+        <v>628031.18960994715</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="2"/>
-        <v>497671.01816535561</v>
+        <v>581510.3607499511</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="2"/>
-        <v>460806.49830125517</v>
+        <v>538435.51921291754</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="2"/>
-        <v>426672.68361227325</v>
+        <v>498551.40667862736</v>
       </c>
       <c r="J11" s="5">
         <f t="shared" si="2"/>
-        <v>395067.29964099376</v>
+        <v>461621.67285058089</v>
       </c>
       <c r="K11" s="5">
         <f t="shared" si="2"/>
-        <v>365803.05522314232</v>
+        <v>427427.47486164898</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="2"/>
-        <v>338706.53261402069</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+        <v>395766.18042745272</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="18"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="18"/>
       <c r="C13" s="2">
         <v>11</v>
@@ -2341,139 +2344,139 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="5">
         <f t="shared" ref="C14:L14" si="3">$C$4/((1+$C$3)^C13)</f>
-        <v>249570.65283337148</v>
+        <v>302403.66006803076</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="3"/>
-        <v>231083.93780867729</v>
+        <v>280003.38895188033</v>
       </c>
       <c r="E14" s="5">
         <f t="shared" si="3"/>
-        <v>213966.6090821086</v>
+        <v>259262.39717766698</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="3"/>
-        <v>198117.230631582</v>
+        <v>240057.77516450643</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="3"/>
-        <v>183441.88021442777</v>
+        <v>222275.71774491333</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="3"/>
-        <v>169853.59279113682</v>
+        <v>205810.84976380866</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="3"/>
-        <v>157271.84517697853</v>
+        <v>190565.60163315616</v>
       </c>
       <c r="J14" s="5">
         <f t="shared" si="3"/>
-        <v>145622.07886757271</v>
+        <v>176449.63114181123</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="3"/>
-        <v>134835.25821071546</v>
+        <v>163379.28809426964</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>124847.46130621801</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+        <v>151277.11860580524</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="18" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="5">
         <f>$C$5/((1+$C$3)^C13)</f>
-        <v>277590.99964343262</v>
+        <v>330424.0068780919</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" ref="D15:K15" si="4">$C$5/((1+$C$3)^D13)</f>
-        <v>257028.70337354869</v>
+        <v>305948.1545167517</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="4"/>
-        <v>237989.54016069323</v>
+        <v>283285.32825625158</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="4"/>
-        <v>220360.68533397515</v>
+        <v>262301.22986689961</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="4"/>
-        <v>204037.67160553255</v>
+        <v>242871.50913601811</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="4"/>
-        <v>188923.77000512273</v>
+        <v>224881.02697779457</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="4"/>
-        <v>174929.41667140994</v>
+        <v>208223.17312758756</v>
       </c>
       <c r="J15" s="5">
         <f t="shared" si="4"/>
-        <v>161971.68210315733</v>
+        <v>192799.23437739586</v>
       </c>
       <c r="K15" s="5">
         <f t="shared" si="4"/>
-        <v>149973.77972514566</v>
+        <v>178517.80960869984</v>
       </c>
       <c r="L15" s="5">
         <f>$C$5/((1+$C$3)^L13)</f>
-        <v>138864.61085661637</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+        <v>165294.26815620359</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="18" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="5">
         <f>$C$6/((1+$C$3)^C13)</f>
-        <v>313617.15982779692</v>
+        <v>366450.16706245625</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" ref="D16:L16" si="5">$C$6/((1+$C$3)^D13)</f>
-        <v>290386.25909981196</v>
+        <v>339305.71024301497</v>
       </c>
       <c r="E16" s="5">
         <f t="shared" si="5"/>
-        <v>268876.16583315923</v>
+        <v>314171.95392871759</v>
       </c>
       <c r="F16" s="5">
         <f t="shared" si="5"/>
-        <v>248959.4128084807</v>
+        <v>290899.9573414051</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="5"/>
-        <v>230517.97482266731</v>
+        <v>269351.8123531529</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" si="5"/>
-        <v>213442.56928024752</v>
+        <v>249399.82625291933</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="5"/>
-        <v>197632.00859282177</v>
+        <v>230925.76504899937</v>
       </c>
       <c r="J16" s="5">
         <f t="shared" si="5"/>
-        <v>182992.60054890902</v>
+        <v>213820.15282314754</v>
       </c>
       <c r="K16" s="5">
         <f t="shared" si="5"/>
-        <v>169437.59310084168</v>
+        <v>197981.62298439586</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="5"/>
-        <v>156886.6602785571</v>
+        <v>183316.31757814431</v>
       </c>
     </row>
   </sheetData>
@@ -2491,13 +2494,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8641AB-FA05-4689-970F-41940E5E4D56}">
   <dimension ref="B1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.35">
       <c r="E1" s="19" t="s">
         <v>63</v>
       </c>
@@ -2511,97 +2514,97 @@
       </c>
       <c r="L1" s="19"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="5">
         <f>'OPEX 15%'!F19</f>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F2" s="11">
         <f>IRR(B9:L9)</f>
-        <v>5.0184901172991569E-2</v>
+        <v>0.11567039840778071</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I2" s="11">
         <f>IRR(B9:Q9)</f>
-        <v>9.7523777393211608E-2</v>
+        <v>0.15342482052643835</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="L2" s="11">
         <f>IRR(B9:V9)</f>
-        <v>0.11489895393710015</v>
-      </c>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+        <v>0.1657690645174994</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="5">
         <f>'OPEX 15%'!I19</f>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F3" s="11">
         <f>IRR(B14:L14)</f>
-        <v>0.15067747468153381</v>
+        <v>0.23247399725711548</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="I3" s="11">
         <f>IRR(B14:Q14)</f>
-        <v>0.18388590121311066</v>
+        <v>0.25665908063956078</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="L3" s="11">
         <f>IRR(B14:V14)</f>
-        <v>0.19400733788652991</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+        <v>0.26278237450593123</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="5">
         <f>'OPEX 15%'!L19</f>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F4" s="11">
         <f>IRR(B19:L19)</f>
-        <v>8.8400235944630756E-2</v>
+        <v>0.15320352828920369</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I4" s="11">
         <f>IRR(B19:Q19)</f>
-        <v>0.12997850894452401</v>
+        <v>0.18609986809100176</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>50</v>
       </c>
       <c r="L4" s="11">
         <f>IRR(B19:V19)</f>
-        <v>0.14427937056240059</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+        <v>0.19607328177660022</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
       <c r="C7" s="19" t="s">
         <v>46</v>
       </c>
@@ -2615,7 +2618,7 @@
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>0</v>
       </c>
@@ -2680,93 +2683,93 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <f>-'CAPEX 15%'!C14</f>
-        <v>-4489312.5</v>
+        <v>-4055562.5</v>
       </c>
       <c r="C9" s="5">
         <f t="shared" ref="C9:V9" si="0">$C$2</f>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="M9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>581908.66666666674</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+        <v>705096.16666666674</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
       <c r="C12" s="19" t="s">
         <v>47</v>
       </c>
@@ -2780,7 +2783,7 @@
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>0</v>
       </c>
@@ -2845,93 +2848,93 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <f>-'CAPEX 15%'!F14</f>
-        <v>-3239987.5</v>
+        <v>-2904237.5</v>
       </c>
       <c r="C14" s="5">
         <f>$C$3</f>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" ref="D14:V14" si="1">$C$3</f>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="E14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="M14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="P14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="S14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="T14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
+        <v>770429.5</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="1"/>
-        <v>647242</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+        <v>770429.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.35">
       <c r="C17" s="19" t="s">
         <v>48</v>
       </c>
@@ -2945,7 +2948,7 @@
       <c r="K17" s="19"/>
       <c r="L17" s="19"/>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>0</v>
       </c>
@@ -3010,90 +3013,90 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B19" s="5">
         <f>-'CAPEX 15%'!I14</f>
-        <v>-4726087.5</v>
+        <v>-4236337.5</v>
       </c>
       <c r="C19" s="5">
         <f>$C$4</f>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" ref="D19:V19" si="2">$C$4</f>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="F19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="H19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="J19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="M19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="N19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="P19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="R19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="S19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="T19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="2"/>
-        <v>731242</v>
+        <v>854429.5</v>
       </c>
     </row>
   </sheetData>
@@ -3112,18 +3115,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8AEBD9-4AB4-44E4-A602-35786004721C}">
   <dimension ref="B2:Y32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>39</v>
       </c>
@@ -3135,17 +3139,17 @@
       </c>
       <c r="F2" s="5">
         <f>'CAPEX 15%'!C14</f>
-        <v>4489312.5</v>
+        <v>4055562.5</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>51</v>
       </c>
       <c r="I2" s="12">
         <f>F2/$C$4</f>
-        <v>7.7148060463096719</v>
-      </c>
-    </row>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
+        <v>5.7517863402557143</v>
+      </c>
+    </row>
+    <row r="3" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>40</v>
       </c>
@@ -3157,58 +3161,58 @@
       </c>
       <c r="F3" s="5">
         <f>'CAPEX 15%'!F14</f>
-        <v>3239987.5</v>
+        <v>2904237.5</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="12">
         <f>F3/$C$5</f>
-        <v>5.0058363023413186</v>
-      </c>
-    </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+        <v>3.7696343403257533</v>
+      </c>
+    </row>
+    <row r="4" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C4" s="5">
         <f>'OPEX 15%'!F19</f>
-        <v>581908.66666666674</v>
+        <v>705096.16666666674</v>
       </c>
       <c r="E4" t="s">
         <v>61</v>
       </c>
       <c r="F4" s="5">
         <f>'CAPEX 15%'!I14</f>
-        <v>4726087.5</v>
+        <v>4236337.5</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I4" s="12">
         <f>F4/$C$6</f>
-        <v>6.4630963484044957</v>
-      </c>
-    </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+        <v>4.958088993884223</v>
+      </c>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="5">
         <f>'OPEX 15%'!I19</f>
-        <v>647242</v>
-      </c>
-    </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+        <v>770429.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5">
         <f>'OPEX 15%'!L19</f>
-        <v>731242</v>
-      </c>
-    </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+        <v>854429.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C7" s="19" t="s">
         <v>51</v>
       </c>
@@ -3234,7 +3238,7 @@
       <c r="X7" s="19"/>
       <c r="Y7" s="19"/>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>0</v>
       </c>
@@ -3299,94 +3303,94 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <f>-F2</f>
-        <v>-4489312.5</v>
+        <v>-4055562.5</v>
       </c>
       <c r="C9" s="5">
         <f>$C$4*C8-$F$2</f>
-        <v>-3907403.833333333</v>
+        <v>-3350466.333333333</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" ref="D9:L9" si="0">$C$4*D8-$F$2</f>
-        <v>-3325495.1666666665</v>
+        <v>-2645370.1666666665</v>
       </c>
       <c r="E9" s="5">
         <f>$C$4*E8-$F$2</f>
-        <v>-2743586.5</v>
+        <v>-1940274</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>-2161677.833333333</v>
+        <v>-1235177.833333333</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>-1579769.166666666</v>
+        <v>-530081.66666666605</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
-        <v>-997860.49999999953</v>
+        <v>175014.5</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>-415951.83333333302</v>
+        <v>880110.66666666698</v>
       </c>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
-        <v>165956.83333333395</v>
+        <v>1585206.833333334</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>747865.50000000093</v>
+        <v>2290303.0000000009</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>1329774.1666666679</v>
+        <v>2995399.1666666679</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="10">
         <f>(C9/$F$2)</f>
-        <v>-0.87037911335718621</v>
+        <v>-0.82614096893669697</v>
       </c>
       <c r="Q9" s="10">
         <f>(D9/$F$2)</f>
-        <v>-0.74075822671437253</v>
+        <v>-0.65228193787339406</v>
       </c>
       <c r="R9" s="10">
         <f t="shared" ref="R9:Y9" si="1">(E9/$F$2)</f>
-        <v>-0.61113734007155884</v>
+        <v>-0.47842290681009109</v>
       </c>
       <c r="S9" s="10">
         <f t="shared" si="1"/>
-        <v>-0.48151645342874505</v>
+        <v>-0.304563875746788</v>
       </c>
       <c r="T9" s="10">
         <f t="shared" si="1"/>
-        <v>-0.35189556678593126</v>
+        <v>-0.13070484468348498</v>
       </c>
       <c r="U9" s="16">
         <f t="shared" si="1"/>
-        <v>-0.22227468014311758</v>
+        <v>4.3154186379817841E-2</v>
       </c>
       <c r="V9" s="10">
         <f t="shared" si="1"/>
-        <v>-9.2653793500303894E-2</v>
+        <v>0.21701321744312088</v>
       </c>
       <c r="W9" s="10">
         <f>(J9/$F$2)</f>
-        <v>3.6967093142509892E-2</v>
+        <v>0.39087224850642394</v>
       </c>
       <c r="X9" s="10">
         <f t="shared" si="1"/>
-        <v>0.16658797978532369</v>
+        <v>0.56473127956972702</v>
       </c>
       <c r="Y9" s="10">
         <f t="shared" si="1"/>
-        <v>0.29620886642813749</v>
-      </c>
-    </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+        <v>0.73859031063303004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C12">
         <v>11</v>
       </c>
@@ -3448,89 +3452,89 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C13" s="5">
         <f>$C$4*C12-$F$2</f>
-        <v>1911682.833333334</v>
+        <v>3700495.333333334</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" ref="D13:L13" si="2">$C$4*D12-$F$2</f>
-        <v>2493591.5000000009</v>
+        <v>4405591.5</v>
       </c>
       <c r="E13" s="5">
         <f t="shared" si="2"/>
-        <v>3075500.1666666679</v>
+        <v>5110687.6666666679</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" si="2"/>
-        <v>3657408.833333334</v>
+        <v>5815783.833333334</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="2"/>
-        <v>4239317.5000000019</v>
+        <v>6520880.0000000019</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="2"/>
-        <v>4821226.1666666679</v>
+        <v>7225976.1666666679</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>5403134.833333334</v>
+        <v>7931072.333333334</v>
       </c>
       <c r="J13" s="5">
         <f t="shared" si="2"/>
-        <v>5985043.5000000019</v>
+        <v>8636168.5000000019</v>
       </c>
       <c r="K13" s="5">
         <f t="shared" si="2"/>
-        <v>6566952.1666666679</v>
+        <v>9341264.6666666679</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="2"/>
-        <v>7148860.8333333358</v>
+        <v>10046360.833333336</v>
       </c>
       <c r="P13" s="10">
         <f>C13/$F$2</f>
-        <v>0.42582975307095106</v>
+        <v>0.91244934169633285</v>
       </c>
       <c r="Q13" s="10">
         <f t="shared" ref="Q13:Y13" si="3">D13/$F$2</f>
-        <v>0.55545063971376485</v>
+        <v>1.0863083727596357</v>
       </c>
       <c r="R13" s="10">
         <f t="shared" si="3"/>
-        <v>0.68507152635657864</v>
+        <v>1.2601674038229389</v>
       </c>
       <c r="S13" s="10">
         <f t="shared" si="3"/>
-        <v>0.81469241299939221</v>
+        <v>1.4340264348862417</v>
       </c>
       <c r="T13" s="10">
         <f t="shared" si="3"/>
-        <v>0.94431329964220623</v>
+        <v>1.607885465949545</v>
       </c>
       <c r="U13" s="10">
         <f t="shared" si="3"/>
-        <v>1.0739341862850198</v>
+        <v>1.781744497012848</v>
       </c>
       <c r="V13" s="10">
         <f t="shared" si="3"/>
-        <v>1.2035550729278335</v>
+        <v>1.9556035280761508</v>
       </c>
       <c r="W13" s="10">
         <f t="shared" si="3"/>
-        <v>1.3331759595706474</v>
+        <v>2.129462559139454</v>
       </c>
       <c r="X13" s="10">
         <f t="shared" si="3"/>
-        <v>1.4627968462134608</v>
+        <v>2.3033215902027568</v>
       </c>
       <c r="Y13" s="16">
         <f t="shared" si="3"/>
-        <v>1.592417732856275</v>
-      </c>
-    </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+        <v>2.4771806212660601</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C16" s="19" t="s">
         <v>52</v>
       </c>
@@ -3556,7 +3560,7 @@
       <c r="X16" s="19"/>
       <c r="Y16" s="19"/>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>0</v>
       </c>
@@ -3621,94 +3625,94 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B18" s="5">
         <f>-F3</f>
-        <v>-3239987.5</v>
+        <v>-2904237.5</v>
       </c>
       <c r="C18" s="5">
         <f t="shared" ref="C18:L18" si="4">$C$5/((1+$C$3)^C17)+B18</f>
-        <v>-2592745.5</v>
+        <v>-2133808</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
-        <v>-1945503.5</v>
+        <v>-1363378.5</v>
       </c>
       <c r="E18" s="5">
         <f t="shared" si="4"/>
-        <v>-1298261.5</v>
+        <v>-592949</v>
       </c>
       <c r="F18" s="5">
         <f t="shared" si="4"/>
-        <v>-651019.5</v>
+        <v>177480.5</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="4"/>
-        <v>-3777.5</v>
+        <v>947910</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="4"/>
-        <v>643464.5</v>
+        <v>1718339.5</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="4"/>
-        <v>1290706.5</v>
+        <v>2488769</v>
       </c>
       <c r="J18" s="5">
         <f t="shared" si="4"/>
-        <v>1937948.5</v>
+        <v>3259198.5</v>
       </c>
       <c r="K18" s="5">
         <f t="shared" si="4"/>
-        <v>2585190.5</v>
+        <v>4029628</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="4"/>
-        <v>3232432.5</v>
+        <v>4800057.5</v>
       </c>
       <c r="O18" s="5"/>
       <c r="P18" s="10">
         <f>C18/$F$3</f>
-        <v>-0.80023317991195952</v>
+        <v>-0.73472228080520274</v>
       </c>
       <c r="Q18" s="10">
         <f t="shared" ref="Q18:Y18" si="5">D18/$F$3</f>
-        <v>-0.60046635982391905</v>
+        <v>-0.46944456161040549</v>
       </c>
       <c r="R18" s="10">
         <f t="shared" si="5"/>
-        <v>-0.40069953973587863</v>
+        <v>-0.20416684241560823</v>
       </c>
       <c r="S18" s="10">
         <f t="shared" si="5"/>
-        <v>-0.20093271964783815</v>
+        <v>6.1110876779189027E-2</v>
       </c>
       <c r="T18" s="16">
         <f t="shared" si="5"/>
-        <v>-1.1658995597976843E-3</v>
+        <v>0.32638859597398628</v>
       </c>
       <c r="U18" s="10">
         <f t="shared" si="5"/>
-        <v>0.19860092052824277</v>
+        <v>0.59166631516878354</v>
       </c>
       <c r="V18" s="10">
         <f t="shared" si="5"/>
-        <v>0.39836774061628322</v>
+        <v>0.8569440343635808</v>
       </c>
       <c r="W18" s="10">
         <f t="shared" si="5"/>
-        <v>0.59813456070432369</v>
+        <v>1.1222217535583781</v>
       </c>
       <c r="X18" s="10">
         <f t="shared" si="5"/>
-        <v>0.79790138079236417</v>
+        <v>1.3874994727531753</v>
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="5"/>
-        <v>0.99766820088040464</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+        <v>1.6527771919479726</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>11</v>
       </c>
@@ -3770,89 +3774,89 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C22" s="5">
         <f>$C$5/((1+$C$3)^C21)+L18</f>
-        <v>3879674.5</v>
+        <v>5570487</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" ref="D22:L22" si="6">$C$5/((1+$C$3)^D21)+C22</f>
-        <v>4526916.5</v>
+        <v>6340916.5</v>
       </c>
       <c r="E22" s="5">
         <f t="shared" si="6"/>
-        <v>5174158.5</v>
+        <v>7111346</v>
       </c>
       <c r="F22" s="5">
         <f t="shared" si="6"/>
-        <v>5821400.5</v>
+        <v>7881775.5</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="6"/>
-        <v>6468642.5</v>
+        <v>8652205</v>
       </c>
       <c r="H22" s="5">
         <f t="shared" si="6"/>
-        <v>7115884.5</v>
+        <v>9422634.5</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="6"/>
-        <v>7763126.5</v>
+        <v>10193064</v>
       </c>
       <c r="J22" s="5">
         <f t="shared" si="6"/>
-        <v>8410368.5</v>
+        <v>10963493.5</v>
       </c>
       <c r="K22" s="5">
         <f t="shared" si="6"/>
-        <v>9057610.5</v>
+        <v>11733923</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="6"/>
-        <v>9704852.5</v>
+        <v>12504352.5</v>
       </c>
       <c r="P22" s="10">
         <f>C22/$F$3</f>
-        <v>1.197435020968445</v>
+        <v>1.9180549111427698</v>
       </c>
       <c r="Q22" s="10">
         <f t="shared" ref="Q22:Y22" si="7">D22/$F$3</f>
-        <v>1.3972018410564855</v>
+        <v>2.1833326303375671</v>
       </c>
       <c r="R22" s="10">
         <f t="shared" si="7"/>
-        <v>1.596968661144526</v>
+        <v>2.4486103495323643</v>
       </c>
       <c r="S22" s="10">
         <f t="shared" si="7"/>
-        <v>1.7967354812325664</v>
+        <v>2.7138880687271616</v>
       </c>
       <c r="T22" s="10">
         <f t="shared" si="7"/>
-        <v>1.9965023013206069</v>
+        <v>2.9791657879219589</v>
       </c>
       <c r="U22" s="10">
         <f t="shared" si="7"/>
-        <v>2.1962691214086476</v>
+        <v>3.2444435071167561</v>
       </c>
       <c r="V22" s="10">
         <f t="shared" si="7"/>
-        <v>2.3960359414966881</v>
+        <v>3.5097212263115534</v>
       </c>
       <c r="W22" s="10">
         <f t="shared" si="7"/>
-        <v>2.5958027615847286</v>
+        <v>3.7749989455063506</v>
       </c>
       <c r="X22" s="10">
         <f t="shared" si="7"/>
-        <v>2.7955695816727686</v>
+        <v>4.0402766647011479</v>
       </c>
       <c r="Y22" s="16">
         <f t="shared" si="7"/>
-        <v>2.9953364017608091</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+        <v>4.3055543838959451</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C26" s="19" t="s">
         <v>53</v>
       </c>
@@ -3878,7 +3882,7 @@
       <c r="X26" s="19"/>
       <c r="Y26" s="19"/>
     </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>0</v>
       </c>
@@ -3943,94 +3947,94 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B28" s="5">
         <f>-F4</f>
-        <v>-4726087.5</v>
+        <v>-4236337.5</v>
       </c>
       <c r="C28" s="5">
         <f t="shared" ref="C28:L28" si="8">$C$6/((1+$C$3)^C27)+B28</f>
-        <v>-3994845.5</v>
+        <v>-3381908</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="8"/>
-        <v>-3263603.5</v>
+        <v>-2527478.5</v>
       </c>
       <c r="E28" s="5">
         <f t="shared" si="8"/>
-        <v>-2532361.5</v>
+        <v>-1673049</v>
       </c>
       <c r="F28" s="5">
         <f t="shared" si="8"/>
-        <v>-1801119.5</v>
+        <v>-818619.5</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="8"/>
-        <v>-1069877.5</v>
+        <v>35810</v>
       </c>
       <c r="H28" s="5">
         <f t="shared" si="8"/>
-        <v>-338635.5</v>
+        <v>890239.5</v>
       </c>
       <c r="I28" s="13">
         <f t="shared" si="8"/>
-        <v>392606.5</v>
+        <v>1744669</v>
       </c>
       <c r="J28" s="5">
         <f t="shared" si="8"/>
-        <v>1123848.5</v>
+        <v>2599098.5</v>
       </c>
       <c r="K28" s="5">
         <f t="shared" si="8"/>
-        <v>1855090.5</v>
+        <v>3453528</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="8"/>
-        <v>2586332.5</v>
+        <v>4307957.5</v>
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="10">
         <f>C28/$F$4</f>
-        <v>-0.84527539957734599</v>
+        <v>-0.79830938871135737</v>
       </c>
       <c r="Q28" s="10">
         <f t="shared" ref="Q28:Y28" si="9">D28/$F$4</f>
-        <v>-0.69055079915469186</v>
+        <v>-0.59661877742271474</v>
       </c>
       <c r="R28" s="10">
         <f t="shared" si="9"/>
-        <v>-0.53582619873203785</v>
+        <v>-0.39492816613407217</v>
       </c>
       <c r="S28" s="10">
         <f t="shared" si="9"/>
-        <v>-0.38110159830938384</v>
+        <v>-0.19323755484542957</v>
       </c>
       <c r="T28" s="10">
         <f t="shared" si="9"/>
-        <v>-0.22637699788672977</v>
+        <v>8.4530564432130344E-3</v>
       </c>
       <c r="U28" s="10">
         <f t="shared" si="9"/>
-        <v>-7.1652397464075729E-2</v>
+        <v>0.21014366773185564</v>
       </c>
       <c r="V28" s="16">
         <f t="shared" si="9"/>
-        <v>8.3072202958578312E-2</v>
+        <v>0.41183427902049824</v>
       </c>
       <c r="W28" s="10">
         <f t="shared" si="9"/>
-        <v>0.23779680338123235</v>
+        <v>0.61352489030914081</v>
       </c>
       <c r="X28" s="10">
         <f t="shared" si="9"/>
-        <v>0.39252140380388639</v>
+        <v>0.81521550159778344</v>
       </c>
       <c r="Y28" s="10">
         <f t="shared" si="9"/>
-        <v>0.54724600422654046</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+        <v>1.0169061128864261</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C31">
         <v>11</v>
       </c>
@@ -4092,86 +4096,86 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.35">
       <c r="C32" s="5">
         <f>$C$6/((1+$C$3)^C31)+L28</f>
-        <v>3317574.5</v>
+        <v>5162387</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32:L32" si="10">$C$6/((1+$C$3)^D31)+C32</f>
-        <v>4048816.5</v>
+        <v>6016816.5</v>
       </c>
       <c r="E32" s="5">
         <f t="shared" si="10"/>
-        <v>4780058.5</v>
+        <v>6871246</v>
       </c>
       <c r="F32" s="5">
         <f t="shared" si="10"/>
-        <v>5511300.5</v>
+        <v>7725675.5</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="10"/>
-        <v>6242542.5</v>
+        <v>8580105</v>
       </c>
       <c r="H32" s="5">
         <f t="shared" si="10"/>
-        <v>6973784.5</v>
+        <v>9434534.5</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="10"/>
-        <v>7705026.5</v>
+        <v>10288964</v>
       </c>
       <c r="J32" s="5">
         <f t="shared" si="10"/>
-        <v>8436268.5</v>
+        <v>11143393.5</v>
       </c>
       <c r="K32" s="5">
         <f t="shared" si="10"/>
-        <v>9167510.5</v>
+        <v>11997823</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="10"/>
-        <v>9898752.5</v>
+        <v>12852252.5</v>
       </c>
       <c r="P32" s="10">
         <f>C32/$F$4</f>
-        <v>0.70197060464919447</v>
+        <v>1.2185967241750686</v>
       </c>
       <c r="Q32" s="10">
         <f t="shared" ref="Q32:Y32" si="11">D32/$F$4</f>
-        <v>0.8566952050718486</v>
+        <v>1.4202873354637113</v>
       </c>
       <c r="R32" s="10">
         <f t="shared" si="11"/>
-        <v>1.0114198054945025</v>
+        <v>1.6219779467523538</v>
       </c>
       <c r="S32" s="10">
         <f t="shared" si="11"/>
-        <v>1.1661444059171566</v>
+        <v>1.8236685580409966</v>
       </c>
       <c r="T32" s="10">
         <f t="shared" si="11"/>
-        <v>1.3208690063398107</v>
+        <v>2.0253591693296391</v>
       </c>
       <c r="U32" s="10">
         <f t="shared" si="11"/>
-        <v>1.4755936067624646</v>
+        <v>2.2270497806182816</v>
       </c>
       <c r="V32" s="10">
         <f t="shared" si="11"/>
-        <v>1.6303182071851188</v>
+        <v>2.4287403919069241</v>
       </c>
       <c r="W32" s="10">
         <f t="shared" si="11"/>
-        <v>1.7850428076077729</v>
+        <v>2.6304310031955671</v>
       </c>
       <c r="X32" s="10">
         <f t="shared" si="11"/>
-        <v>1.9397674080304268</v>
+        <v>2.8321216144842096</v>
       </c>
       <c r="Y32" s="16">
         <f t="shared" si="11"/>
-        <v>2.0944920084530807</v>
+        <v>3.0338122257728521</v>
       </c>
     </row>
   </sheetData>
